--- a/03_CAD/URDF/matt_robodog_rev00/reference/Coordinate_Cinematiche_matt_robodog_rev00.xlsx
+++ b/03_CAD/URDF/matt_robodog_rev00/reference/Coordinate_Cinematiche_matt_robodog_rev00.xlsx
@@ -2,13 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Joint_Parameters" sheetId="1" r:id="R934edb50362e4964"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mesh_Transforms" sheetId="2" r:id="R26da9648eeeb444b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Notes" sheetId="3" r:id="Rf0e4cb9402584a51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Link_Engineering" sheetId="4" r:id="R37f63bafa818485f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mass_Summary" sheetId="5" r:id="R9fa04e4e118842f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engineering_Weight_Source" sheetId="6" r:id="Ra9f7c32ad07b4f09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="URDF_Audit" sheetId="7" r:id="R4acc96da8fb04a92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Joint_Parameters" sheetId="1" r:id="R1aef14a5ec6a4b2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mesh_Transforms" sheetId="2" r:id="R55c82896a21a4ba6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Notes" sheetId="3" r:id="Rbf13f7eeb9bc484d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Link_Engineering" sheetId="4" r:id="R4f9575abea25442e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mass_Summary" sheetId="5" r:id="Rbb5f3fdc6baa40a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engineering_Weight_Source" sheetId="6" r:id="R58c9dcc699854f93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="URDF_Audit" sheetId="7" r:id="R36b9bd6648a0444c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inertial_Properties" sheetId="8" r:id="Rc52f2c3cd0764fe5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAD_Source_Data" sheetId="9" r:id="Re29c0b12f341438a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mass_Reconciliation" sheetId="10" r:id="Rf788816304f64b13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physical_Property_Method" sheetId="11" r:id="Re58eb096c8f14ec6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,13 +23,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="200" formatCode="0.0"/>
     <x:numFmt numFmtId="201" formatCode="0.0000"/>
     <x:numFmt numFmtId="202" formatCode="0.000000"/>
     <x:numFmt numFmtId="203" formatCode="0.000000000000000"/>
+    <x:numFmt numFmtId="204" formatCode="0.0000000000"/>
+    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="206" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="16">
+  <x:fonts count="21">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -120,8 +127,36 @@
       <x:color rgb="FF1F2937"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F1F1F"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF9C0006"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F1F1F"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF7F6000"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF006100"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="23">
+  <x:fills count="30">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -233,6 +268,41 @@
         <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF5B9BD5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAD3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="10">
     <x:border/>
@@ -249,7 +319,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="286">
+  <x:cellXfs count="393">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -946,6 +1016,307 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="18" fillId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="18" fillId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="18" fillId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="3" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -957,7 +1328,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -968,7 +1339,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -2607,8 +2978,482 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec64f17a11314d07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ecf6a50657d4585"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="36" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="289" t="str">
+        <x:v>MATDOG — Riconciliazione masse REV00</x:v>
+      </x:c>
+      <x:c r="B1" s="289"/>
+      <x:c r="C1" s="289"/>
+      <x:c r="D1" s="289"/>
+      <x:c r="E1" s="289"/>
+      <x:c r="F1" s="289"/>
+      <x:c r="G1" s="289"/>
+      <x:c r="H1" s="289"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="294" t="str">
+        <x:v>Il modello dinamico usa le masse CAD per-link che riconciliano esattamente i 2.480 kg dell’assieme CAD. Il peso calcolato e la misura reale sono conservati come controlli di configurazione, non come scala automatica del tensore d’inerzia.</x:v>
+      </x:c>
+      <x:c r="B2" s="294"/>
+      <x:c r="C2" s="294"/>
+      <x:c r="D2" s="294"/>
+      <x:c r="E2" s="294"/>
+      <x:c r="F2" s="294"/>
+      <x:c r="G2" s="294"/>
+      <x:c r="H2" s="294"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="300" t="str">
+        <x:v>Metric</x:v>
+      </x:c>
+      <x:c r="B4" s="300" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="301" t="str">
+        <x:v>URDF dynamic model — CAD mass [kg]</x:v>
+      </x:c>
+      <x:c r="B5" s="306" t="n">
+        <x:v>2.48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="301" t="str">
+        <x:v>CAD full assembly report [kg]</x:v>
+      </x:c>
+      <x:c r="B6" s="306" t="n">
+        <x:v>2.48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="301" t="str">
+        <x:v>Difference model vs full CAD [kg]</x:v>
+      </x:c>
+      <x:c r="B7" s="306" t="n">
+        <x:f>B5-B6</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="301" t="str">
+        <x:v>Weight-breakdown calculated [kg]</x:v>
+      </x:c>
+      <x:c r="B8" s="306" t="n">
+        <x:v>2.3894</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="301" t="str">
+        <x:v>Physical robot measured [kg]</x:v>
+      </x:c>
+      <x:c r="B9" s="306" t="n">
+        <x:v>2.297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="301" t="str">
+        <x:v>CAD model − measured robot [kg]</x:v>
+      </x:c>
+      <x:c r="B10" s="306" t="n">
+        <x:f>B5-B9</x:f>
+        <x:v>0.18299999999999983</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="301" t="str">
+        <x:v>CAD model − measured robot [%]</x:v>
+      </x:c>
+      <x:c r="B11" s="308" t="n">
+        <x:f>(B5-B9)/B5</x:f>
+        <x:v>0.07379032258064509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="301" t="str">
+        <x:v>Neck yaw actuator [kg]</x:v>
+      </x:c>
+      <x:c r="B12" s="306" t="n">
+        <x:v>0.061</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="310" t="str">
+        <x:v>Neck yaw actuator in REV00 17-link URDF</x:v>
+      </x:c>
+      <x:c r="B13" s="310" t="str">
+        <x:v>No standalone link; not added without a dedicated mounted-frame CAD report.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="300" t="str">
+        <x:v>Link family</x:v>
+      </x:c>
+      <x:c r="B16" s="300" t="str">
+        <x:v>Quantity</x:v>
+      </x:c>
+      <x:c r="C16" s="300" t="str">
+        <x:v>CAD mass / unit [kg]</x:v>
+      </x:c>
+      <x:c r="D16" s="300" t="str">
+        <x:v>CAD group [kg]</x:v>
+      </x:c>
+      <x:c r="E16" s="300" t="str">
+        <x:v>Weight breakdown / unit [kg]</x:v>
+      </x:c>
+      <x:c r="F16" s="300" t="str">
+        <x:v>Weight breakdown group [kg]</x:v>
+      </x:c>
+      <x:c r="G16" s="300" t="str">
+        <x:v>CAD − breakdown [kg]</x:v>
+      </x:c>
+      <x:c r="H16" s="300" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="301" t="str">
+        <x:v>base_link</x:v>
+      </x:c>
+      <x:c r="B17" s="301" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="306" t="n">
+        <x:v>1.282</x:v>
+      </x:c>
+      <x:c r="D17" s="306" t="n">
+        <x:f>B17*C17</x:f>
+        <x:v>1.282</x:v>
+      </x:c>
+      <x:c r="E17" s="306" t="n">
+        <x:v>1.237</x:v>
+      </x:c>
+      <x:c r="F17" s="306" t="n">
+        <x:f>B17*E17</x:f>
+        <x:v>1.237</x:v>
+      </x:c>
+      <x:c r="G17" s="306" t="n">
+        <x:f>D17-F17</x:f>
+        <x:v>0.04499999999999993</x:v>
+      </x:c>
+      <x:c r="H17" s="301" t="str">
+        <x:v>CAD direct</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="301" t="str">
+        <x:v>hip_link</x:v>
+      </x:c>
+      <x:c r="B18" s="301" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C18" s="306" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="D18" s="306" t="n">
+        <x:f>B18*C18</x:f>
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="E18" s="306" t="n">
+        <x:v>0.0506</x:v>
+      </x:c>
+      <x:c r="F18" s="306" t="n">
+        <x:f>B18*E18</x:f>
+        <x:v>0.2024</x:v>
+      </x:c>
+      <x:c r="G18" s="306" t="n">
+        <x:f>D18-F18</x:f>
+        <x:v>-0.0023999999999999855</x:v>
+      </x:c>
+      <x:c r="H18" s="301" t="str">
+        <x:v>CAD direct / link CAD report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="301" t="str">
+        <x:v>upper_leg_link</x:v>
+      </x:c>
+      <x:c r="B19" s="301" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="306" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="D19" s="306" t="n">
+        <x:f>B19*C19</x:f>
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="E19" s="306" t="n">
+        <x:v>0.1597</x:v>
+      </x:c>
+      <x:c r="F19" s="306" t="n">
+        <x:f>B19*E19</x:f>
+        <x:v>0.6388</x:v>
+      </x:c>
+      <x:c r="G19" s="306" t="n">
+        <x:f>D19-F19</x:f>
+        <x:v>0.05119999999999991</x:v>
+      </x:c>
+      <x:c r="H19" s="301" t="str">
+        <x:v>CAD direct / link CAD report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="301" t="str">
+        <x:v>lower_leg_link</x:v>
+      </x:c>
+      <x:c r="B20" s="301" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="306" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="D20" s="306" t="n">
+        <x:f>B20*C20</x:f>
+        <x:v>0.238</x:v>
+      </x:c>
+      <x:c r="E20" s="306" t="n">
+        <x:v>0.0628</x:v>
+      </x:c>
+      <x:c r="F20" s="306" t="n">
+        <x:f>B20*E20</x:f>
+        <x:v>0.2512</x:v>
+      </x:c>
+      <x:c r="G20" s="306" t="n">
+        <x:f>D20-F20</x:f>
+        <x:v>-0.01319999999999999</x:v>
+      </x:c>
+      <x:c r="H20" s="301" t="str">
+        <x:v>CAD direct / link CAD report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="301" t="str">
+        <x:v>foot_link</x:v>
+      </x:c>
+      <x:c r="B21" s="301" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="306" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="D21" s="306" t="n">
+        <x:f>B21*C21</x:f>
+        <x:v>0.07</x:v>
+      </x:c>
+      <x:c r="E21" s="306" t="n">
+        <x:v>0.015</x:v>
+      </x:c>
+      <x:c r="F21" s="306" t="n">
+        <x:f>B21*E21</x:f>
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="G21" s="306" t="n">
+        <x:f>D21-F21</x:f>
+        <x:v>0.010000000000000009</x:v>
+      </x:c>
+      <x:c r="H21" s="301" t="str">
+        <x:v>CAD direct / link CAD report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="317" t="str">
+        <x:v>TOTAL</x:v>
+      </x:c>
+      <x:c r="B22" s="317"/>
+      <x:c r="C22" s="318"/>
+      <x:c r="D22" s="318" t="n">
+        <x:f>SUM(D17:D21)</x:f>
+        <x:v>2.4799999999999995</x:v>
+      </x:c>
+      <x:c r="E22" s="318"/>
+      <x:c r="F22" s="318" t="n">
+        <x:f>SUM(F17:F21)</x:f>
+        <x:v>2.3893999999999997</x:v>
+      </x:c>
+      <x:c r="G22" s="318" t="n">
+        <x:f>D22-F22</x:f>
+        <x:v>0.09059999999999979</x:v>
+      </x:c>
+      <x:c r="H22" s="317" t="str">
+        <x:v>Reconciled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="322" t="str">
+        <x:v>Interpretation: the 2.480 kg URDF baseline is internally CAD-consistent. The 2.297 kg physical weighing differs by 0.183 kg; the supplied inputs do not allocate that difference link by link, so no global inertia scaling has been applied. Create a separate configuration only after weighing the installed hardware with an explicit component inventory.</x:v>
+      </x:c>
+      <x:c r="B24" s="322"/>
+      <x:c r="C24" s="322"/>
+      <x:c r="D24" s="322"/>
+      <x:c r="E24" s="322"/>
+      <x:c r="F24" s="322"/>
+      <x:c r="G24" s="322"/>
+      <x:c r="H24" s="322"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="322"/>
+      <x:c r="B25" s="322"/>
+      <x:c r="C25" s="322"/>
+      <x:c r="D25" s="322"/>
+      <x:c r="E25" s="322"/>
+      <x:c r="F25" s="322"/>
+      <x:c r="G25" s="322"/>
+      <x:c r="H25" s="322"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A24:H25"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="110" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="289" t="str">
+        <x:v>MATDOG — Metodo di conversione CAD → URDF &lt;inertial&gt;</x:v>
+      </x:c>
+      <x:c r="B1" s="289"/>
+      <x:c r="C1" s="289"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="294" t="str">
+        <x:v>Questa pagina descrive il metodo ripetibile usato per trasformare i report Solid Edge nei campi standard URDF, senza introdurre inerzie fittizie.</x:v>
+      </x:c>
+      <x:c r="B2" s="294"/>
+      <x:c r="C2" s="294"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="300" t="str">
+        <x:v>Step</x:v>
+      </x:c>
+      <x:c r="B4" s="300" t="str">
+        <x:v>Engineering decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="317" t="str">
+        <x:v>1. Data scope</x:v>
+      </x:c>
+      <x:c r="B5" s="301" t="str">
+        <x:v>Base link and LF subassemblies were exported from Solid Edge. The CAD report prints CoM coordinates, principal-axis directions and radii of gyration. The full robot assembly report is used only as an aggregate validation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="317" t="str">
+        <x:v>2. Mass source</x:v>
+      </x:c>
+      <x:c r="B6" s="301" t="str">
+        <x:v>URDF masses use the higher-precision CAD values from weight_breakdown_summary.txt: base 1.282 kg, hip 0.050 kg, upper 0.1725 kg, lower 0.0595 kg and foot 0.0175 kg. These sum to 2.480 kg.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="317" t="str">
+        <x:v>3. CoM source</x:v>
+      </x:c>
+      <x:c r="B7" s="301" t="str">
+        <x:v>Each direct CAD report provides the link CoM in millimetres. The values are converted to metres and used as &lt;inertial&gt;&lt;origin xyz=...&gt;.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="317" t="str">
+        <x:v>4. Inertia construction</x:v>
+      </x:c>
+      <x:c r="B8" s="301" t="str">
+        <x:v>The direct global-origin inertia entries are rounded in the text exports. To avoid parallel-axis rounding loss, the final inertia tensor is reconstructed at the CoM from principal axes and radii of gyration: I_C = Rᵀ diag(m·K₁², m·K₂², m·K₃²) R.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="317" t="str">
+        <x:v>5. Axis cleanup</x:v>
+      </x:c>
+      <x:c r="B9" s="301" t="str">
+        <x:v>The exported principal-axis vectors are rounded to three decimals. Each 3×3 direction-cosine matrix is orthonormalized to the nearest right-handed rotation before tensor reconstruction.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="317" t="str">
+        <x:v>6. Right-side derivation</x:v>
+      </x:c>
+      <x:c r="B10" s="301" t="str">
+        <x:v>RF and RH hip/upper/lower properties are produced by local Y reflection: M = diag(1, −1, 1); CoM' = M·CoM and I' = M·I·Mᵀ.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="317" t="str">
+        <x:v>7. Rear / foot derivation</x:v>
+      </x:c>
+      <x:c r="B11" s="301" t="str">
+        <x:v>LH uses the same left-side local geometry as LF. The CAD foot geometry is identical for all four legs; the LF foot tensor is reused. The aggregate assembly check validates these substitutions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="317" t="str">
+        <x:v>8. Aggregate validation</x:v>
+      </x:c>
+      <x:c r="B12" s="301" t="str">
+        <x:v>Rebuilt 17-link model: 2.480 kg, CoM = [9.571, −0.336, 5.970] mm. CAD assembly: 2.480 kg, CoM = [9.480, −0.710, 5.910] mm. Largest CoM deviation is 0.374 mm.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="317" t="str">
+        <x:v>9. Product-of-inertia convention</x:v>
+      </x:c>
+      <x:c r="B13" s="301" t="str">
+        <x:v>Solid Edge lists products of inertia. URDF &lt;inertia&gt; uses tensor off-diagonal entries; the assembly principal-axis check validates the sign used in the reconstructed tensor. The final values stored in Inertial_Properties are the actual tensor entries.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="317" t="str">
+        <x:v>10. Neck yaw actuator</x:v>
+      </x:c>
+      <x:c r="B14" s="301" t="str">
+        <x:v>The provided assembly-scope note says the neck yaw actuator is not included as a standalone modeled component. REV00 remains 17 links and does not add an unlocated 0.061 kg mass. Add it only after exporting its mounted CAD subassembly or creating a fixed neck link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="317" t="str">
+        <x:v>11. Simulation scope</x:v>
+      </x:c>
+      <x:c r="B15" s="301" t="str">
+        <x:v>The resulting URDF is suitable for future rigid-body simulation of the 17-link CAD configuration. Current external-power/no-battery hardware should be represented by a separate configuration rather than modifying this CAD baseline ad hoc.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:C1"/>
+    <x:mergeCell ref="A2:C2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -2631,1360 +3476,1360 @@
     <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="10" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="11" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="42" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="38" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="33" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="16" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="16" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="31" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="13" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="28" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="48" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="22" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="22" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="22" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="139" t="str">
-        <x:v>MATDOG — Trasformazioni mesh Visual + Collision + proprietà di massa</x:v>
-      </x:c>
-      <x:c r="B1" s="139"/>
-      <x:c r="C1" s="139"/>
-      <x:c r="D1" s="139"/>
-      <x:c r="E1" s="139"/>
-      <x:c r="F1" s="139"/>
-      <x:c r="G1" s="139"/>
-      <x:c r="H1" s="139"/>
-      <x:c r="I1" s="139"/>
-      <x:c r="J1" s="139"/>
-      <x:c r="K1" s="139"/>
-      <x:c r="L1" s="139"/>
-      <x:c r="M1" s="139"/>
-      <x:c r="N1" s="139"/>
-      <x:c r="O1" s="139"/>
-      <x:c r="P1" s="139"/>
-      <x:c r="Q1" s="139"/>
-      <x:c r="R1" s="139"/>
-      <x:c r="S1" s="139"/>
-      <x:c r="T1" s="139"/>
-      <x:c r="U1" s="139"/>
-      <x:c r="V1" s="139"/>
-      <x:c r="W1" s="139"/>
-    </x:row>
-    <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="144" t="str">
-        <x:v>Masse reali da Engineering_Data.xlsx / Weight. Trasformazioni audit: tutte le mesh sono zero eccetto le 4 upper leg, che usano la forma equivalente minima xyz = 0,0,-0.090 m · rpy = 0°,180°,0°.</x:v>
-      </x:c>
-      <x:c r="B2" s="144"/>
-      <x:c r="C2" s="144"/>
-      <x:c r="D2" s="144"/>
-      <x:c r="E2" s="144"/>
-      <x:c r="F2" s="144"/>
-      <x:c r="G2" s="144"/>
-      <x:c r="H2" s="144"/>
-      <x:c r="I2" s="144"/>
-      <x:c r="J2" s="144"/>
-      <x:c r="K2" s="144"/>
-      <x:c r="L2" s="144"/>
-      <x:c r="M2" s="144"/>
-      <x:c r="N2" s="144"/>
-      <x:c r="O2" s="144"/>
-      <x:c r="P2" s="144"/>
-      <x:c r="Q2" s="144"/>
-      <x:c r="R2" s="144"/>
-      <x:c r="S2" s="144"/>
-      <x:c r="T2" s="144"/>
-      <x:c r="U2" s="144"/>
-      <x:c r="V2" s="144"/>
-      <x:c r="W2" s="144"/>
+      <x:c r="A1" s="289" t="str">
+        <x:v>MATDOG — Mesh Visual + Collision + proprietà dinamiche</x:v>
+      </x:c>
+      <x:c r="B1" s="289"/>
+      <x:c r="C1" s="289"/>
+      <x:c r="D1" s="289"/>
+      <x:c r="E1" s="289"/>
+      <x:c r="F1" s="289"/>
+      <x:c r="G1" s="289"/>
+      <x:c r="H1" s="289"/>
+      <x:c r="I1" s="289"/>
+      <x:c r="J1" s="289"/>
+      <x:c r="K1" s="289"/>
+      <x:c r="L1" s="289"/>
+      <x:c r="M1" s="289"/>
+      <x:c r="N1" s="289"/>
+      <x:c r="O1" s="289"/>
+      <x:c r="P1" s="289"/>
+      <x:c r="Q1" s="289"/>
+      <x:c r="R1" s="289"/>
+      <x:c r="S1" s="289"/>
+      <x:c r="T1" s="289"/>
+      <x:c r="U1" s="289"/>
+      <x:c r="V1" s="289"/>
+      <x:c r="W1" s="289"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="294" t="str">
+        <x:v>Origini mesh visual/collision: xyz = 0,0,0 m · rpy = 0°,0°,0°. Le colonne di massa e stato inerziale sono aggiornate dal modello CAD dinamico REV00.</x:v>
+      </x:c>
+      <x:c r="B2" s="294"/>
+      <x:c r="C2" s="294"/>
+      <x:c r="D2" s="294"/>
+      <x:c r="E2" s="294"/>
+      <x:c r="F2" s="294"/>
+      <x:c r="G2" s="294"/>
+      <x:c r="H2" s="294"/>
+      <x:c r="I2" s="294"/>
+      <x:c r="J2" s="294"/>
+      <x:c r="K2" s="294"/>
+      <x:c r="L2" s="294"/>
+      <x:c r="M2" s="294"/>
+      <x:c r="N2" s="294"/>
+      <x:c r="O2" s="294"/>
+      <x:c r="P2" s="294"/>
+      <x:c r="Q2" s="294"/>
+      <x:c r="R2" s="294"/>
+      <x:c r="S2" s="294"/>
+      <x:c r="T2" s="294"/>
+      <x:c r="U2" s="294"/>
+      <x:c r="V2" s="294"/>
+      <x:c r="W2" s="294"/>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="36" t="str">
+      <x:c r="A5" s="345" t="str">
         <x:v>Link</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="str">
+      <x:c r="B5" s="345" t="str">
         <x:v>Visual mesh</x:v>
       </x:c>
-      <x:c r="C5" s="36" t="str">
+      <x:c r="C5" s="345" t="str">
         <x:v>Collision mesh</x:v>
       </x:c>
-      <x:c r="D5" s="36" t="str">
+      <x:c r="D5" s="345" t="str">
         <x:v>Visual X
 [m]</x:v>
       </x:c>
-      <x:c r="E5" s="36" t="str">
+      <x:c r="E5" s="345" t="str">
         <x:v>Visual Y
 [m]</x:v>
       </x:c>
-      <x:c r="F5" s="36" t="str">
+      <x:c r="F5" s="345" t="str">
         <x:v>Visual Z
 [m]</x:v>
       </x:c>
-      <x:c r="G5" s="36" t="str">
+      <x:c r="G5" s="345" t="str">
         <x:v>Visual R
 [deg]</x:v>
       </x:c>
-      <x:c r="H5" s="36" t="str">
+      <x:c r="H5" s="345" t="str">
         <x:v>Visual P
 [deg]</x:v>
       </x:c>
-      <x:c r="I5" s="36" t="str">
+      <x:c r="I5" s="345" t="str">
         <x:v>Visual Yaw
 [deg]</x:v>
       </x:c>
-      <x:c r="J5" s="36" t="str">
+      <x:c r="J5" s="345" t="str">
         <x:v>Collision X
 [m]</x:v>
       </x:c>
-      <x:c r="K5" s="36" t="str">
+      <x:c r="K5" s="345" t="str">
         <x:v>Collision Y
 [m]</x:v>
       </x:c>
-      <x:c r="L5" s="36" t="str">
+      <x:c r="L5" s="345" t="str">
         <x:v>Collision Z
 [m]</x:v>
       </x:c>
-      <x:c r="M5" s="36" t="str">
+      <x:c r="M5" s="345" t="str">
         <x:v>Collision R
 [deg]</x:v>
       </x:c>
-      <x:c r="N5" s="36" t="str">
+      <x:c r="N5" s="345" t="str">
         <x:v>Collision P
 [deg]</x:v>
       </x:c>
-      <x:c r="O5" s="36" t="str">
+      <x:c r="O5" s="345" t="str">
         <x:v>Collision Yaw
 [deg]</x:v>
       </x:c>
-      <x:c r="P5" s="157" t="str">
+      <x:c r="P5" s="345" t="str">
         <x:v>Mass
 [g]</x:v>
       </x:c>
-      <x:c r="Q5" s="158" t="str">
+      <x:c r="Q5" s="345" t="str">
         <x:v>Mass
 [kg]</x:v>
       </x:c>
-      <x:c r="R5" s="158" t="str">
+      <x:c r="R5" s="345" t="str">
         <x:v>Engineering material / composition</x:v>
       </x:c>
-      <x:c r="S5" s="158" t="str">
+      <x:c r="S5" s="345" t="str">
         <x:v>Weight roll-up components</x:v>
       </x:c>
-      <x:c r="T5" s="158" t="str">
+      <x:c r="T5" s="345" t="str">
         <x:v>Fastener allocation</x:v>
       </x:c>
-      <x:c r="U5" s="158" t="str">
+      <x:c r="U5" s="345" t="str">
         <x:v>CoM status</x:v>
       </x:c>
-      <x:c r="V5" s="158" t="str">
+      <x:c r="V5" s="345" t="str">
         <x:v>Inertia status</x:v>
       </x:c>
-      <x:c r="W5" s="159" t="str">
+      <x:c r="W5" s="345" t="str">
         <x:v>URDF metadata</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="19" customHeight="1">
-      <x:c r="A6" s="43" t="str">
+      <x:c r="A6" s="359" t="str">
         <x:v>base_link</x:v>
       </x:c>
-      <x:c r="B6" s="43" t="str">
+      <x:c r="B6" s="359" t="str">
         <x:v>meshes/base_link.stl</x:v>
       </x:c>
-      <x:c r="C6" s="43" t="str">
+      <x:c r="C6" s="359" t="str">
         <x:v>meshes/base_link.stl</x:v>
       </x:c>
-      <x:c r="D6" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E6" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F6" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I6" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J6" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K6" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L6" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M6" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O6" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P6" s="168" t="n">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="Q6" s="169" t="n">
-        <x:v>0.285</x:v>
-      </x:c>
-      <x:c r="R6" s="170" t="str">
-        <x:v>PPA+CF (283 g); Steel fasteners (2 g)</x:v>
-      </x:c>
-      <x:c r="S6" s="170" t="str">
-        <x:v>Lower_Chassis 283 g + Fasteners 2 g</x:v>
-      </x:c>
-      <x:c r="T6" s="170" t="str">
-        <x:v>2 g assigned directly to base_link</x:v>
-      </x:c>
-      <x:c r="U6" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V6" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W6" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D6" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J6" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L6" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N6" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O6" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" s="306" t="n">
+        <x:v>1282</x:v>
+      </x:c>
+      <x:c r="Q6" s="306" t="n">
+        <x:v>1.282</x:v>
+      </x:c>
+      <x:c r="R6" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S6" s="301" t="str">
+        <x:v>physprop__base_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T6" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U6" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V6" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W6" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="19" customHeight="1">
-      <x:c r="A7" s="43" t="str">
+      <x:c r="A7" s="359" t="str">
         <x:v>lf_hip_link</x:v>
       </x:c>
-      <x:c r="B7" s="43" t="str">
+      <x:c r="B7" s="359" t="str">
         <x:v>meshes/lf_hip_link.stl</x:v>
       </x:c>
-      <x:c r="C7" s="43" t="str">
+      <x:c r="C7" s="359" t="str">
         <x:v>meshes/lf_hip_link.stl</x:v>
       </x:c>
-      <x:c r="D7" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E7" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F7" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I7" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L7" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M7" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O7" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P7" s="168" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Q7" s="169" t="n">
-        <x:v>0.097</x:v>
-      </x:c>
-      <x:c r="R7" s="170" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); Steel fasteners (4 g)</x:v>
-      </x:c>
-      <x:c r="S7" s="170" t="str">
-        <x:v>ACT_FL_Shoulder + Shoulder_Joint_L + leg fasteners</x:v>
-      </x:c>
-      <x:c r="T7" s="170" t="str">
-        <x:v>4 g leg fasteners provisionally allocated to hip_link</x:v>
-      </x:c>
-      <x:c r="U7" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V7" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W7" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D7" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J7" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="306" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q7" s="306" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="R7" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S7" s="301" t="str">
+        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T7" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U7" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V7" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W7" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="19" customHeight="1">
-      <x:c r="A8" s="82" t="str">
+      <x:c r="A8" s="362" t="str">
         <x:v>lf_upper_leg_link</x:v>
       </x:c>
-      <x:c r="B8" s="82" t="str">
+      <x:c r="B8" s="362" t="str">
         <x:v>meshes/lf_upper_leg_link.stl</x:v>
       </x:c>
-      <x:c r="C8" s="82" t="str">
+      <x:c r="C8" s="362" t="str">
         <x:v>meshes/lf_upper_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D8" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E8" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" s="84" t="n">
-        <x:v>-0.09</x:v>
-      </x:c>
-      <x:c r="G8" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H8" s="86" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="I8" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J8" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L8" s="84" t="n">
-        <x:v>-0.09</x:v>
-      </x:c>
-      <x:c r="M8" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="86" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="O8" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P8" s="168" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="Q8" s="169" t="n">
-        <x:v>0.098</x:v>
-      </x:c>
-      <x:c r="R8" s="170" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); ABS ESD cover (5 g)</x:v>
-      </x:c>
-      <x:c r="S8" s="170" t="str">
-        <x:v>ACT_FL_UpperLeg + Upper_Leg + Upper_Leg_Cover</x:v>
-      </x:c>
-      <x:c r="T8" s="170" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="U8" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V8" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W8" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D8" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L8" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="306" t="n">
+        <x:v>172.5</x:v>
+      </x:c>
+      <x:c r="Q8" s="306" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="R8" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S8" s="301" t="str">
+        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T8" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U8" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V8" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W8" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="19" customHeight="1">
-      <x:c r="A9" s="43" t="str">
+      <x:c r="A9" s="359" t="str">
         <x:v>lf_lower_leg_link</x:v>
       </x:c>
-      <x:c r="B9" s="43" t="str">
+      <x:c r="B9" s="359" t="str">
         <x:v>meshes/lf_lower_leg_link.stl</x:v>
       </x:c>
-      <x:c r="C9" s="43" t="str">
+      <x:c r="C9" s="359" t="str">
         <x:v>meshes/lf_lower_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D9" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E9" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I9" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K9" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L9" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M9" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O9" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P9" s="168" t="n">
-        <x:v>114.5</x:v>
-      </x:c>
-      <x:c r="Q9" s="169" t="n">
-        <x:v>0.1145</x:v>
-      </x:c>
-      <x:c r="R9" s="170" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (53.5 g)</x:v>
-      </x:c>
-      <x:c r="S9" s="170" t="str">
-        <x:v>ACT_FL_LowerLeg + Lower_Leg_L</x:v>
-      </x:c>
-      <x:c r="T9" s="170" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="U9" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V9" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W9" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D9" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O9" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P9" s="306" t="n">
+        <x:v>59.5</x:v>
+      </x:c>
+      <x:c r="Q9" s="306" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="R9" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S9" s="301" t="str">
+        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T9" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U9" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V9" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W9" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="19" customHeight="1">
-      <x:c r="A10" s="43" t="str">
+      <x:c r="A10" s="359" t="str">
         <x:v>lf_foot_link</x:v>
       </x:c>
-      <x:c r="B10" s="43" t="str">
+      <x:c r="B10" s="359" t="str">
         <x:v>meshes/lf_foot_link.stl</x:v>
       </x:c>
-      <x:c r="C10" s="43" t="str">
+      <x:c r="C10" s="359" t="str">
         <x:v>meshes/lf_foot_link.stl</x:v>
       </x:c>
-      <x:c r="D10" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E10" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F10" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H10" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I10" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J10" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K10" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L10" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M10" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O10" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P10" s="168" t="n">
-        <x:v>6.5</x:v>
-      </x:c>
-      <x:c r="Q10" s="169" t="n">
-        <x:v>0.0065</x:v>
-      </x:c>
-      <x:c r="R10" s="170" t="str">
-        <x:v>TPU 95A (6.5 g)</x:v>
-      </x:c>
-      <x:c r="S10" s="170" t="str">
-        <x:v>Rubber_Foot FL</x:v>
-      </x:c>
-      <x:c r="T10" s="170" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="U10" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V10" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W10" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D10" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J10" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O10" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" s="306" t="n">
+        <x:v>17.5</x:v>
+      </x:c>
+      <x:c r="Q10" s="306" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="R10" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S10" s="301" t="str">
+        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T10" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U10" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V10" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W10" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="19" customHeight="1">
-      <x:c r="A11" s="43" t="str">
+      <x:c r="A11" s="359" t="str">
         <x:v>rf_hip_link</x:v>
       </x:c>
-      <x:c r="B11" s="43" t="str">
+      <x:c r="B11" s="359" t="str">
         <x:v>meshes/rf_hip_link.stl</x:v>
       </x:c>
-      <x:c r="C11" s="43" t="str">
+      <x:c r="C11" s="359" t="str">
         <x:v>meshes/rf_hip_link.stl</x:v>
       </x:c>
-      <x:c r="D11" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E11" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F11" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I11" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L11" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M11" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O11" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P11" s="168" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Q11" s="169" t="n">
-        <x:v>0.097</x:v>
-      </x:c>
-      <x:c r="R11" s="170" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); Steel fasteners (4 g)</x:v>
-      </x:c>
-      <x:c r="S11" s="170" t="str">
-        <x:v>ACT_FR_Shoulder + Shoulder_Joint_R + leg fasteners</x:v>
-      </x:c>
-      <x:c r="T11" s="170" t="str">
-        <x:v>4 g leg fasteners provisionally allocated to hip_link</x:v>
-      </x:c>
-      <x:c r="U11" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V11" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W11" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D11" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L11" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N11" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" s="306" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q11" s="306" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="R11" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S11" s="301" t="str">
+        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T11" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U11" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V11" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W11" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="19" customHeight="1">
-      <x:c r="A12" s="82" t="str">
+      <x:c r="A12" s="362" t="str">
         <x:v>rf_upper_leg_link</x:v>
       </x:c>
-      <x:c r="B12" s="82" t="str">
+      <x:c r="B12" s="362" t="str">
         <x:v>meshes/rf_upper_leg_link.stl</x:v>
       </x:c>
-      <x:c r="C12" s="82" t="str">
+      <x:c r="C12" s="362" t="str">
         <x:v>meshes/rf_upper_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D12" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F12" s="84" t="n">
-        <x:v>-0.09</x:v>
-      </x:c>
-      <x:c r="G12" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H12" s="86" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="I12" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J12" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K12" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L12" s="84" t="n">
-        <x:v>-0.09</x:v>
-      </x:c>
-      <x:c r="M12" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="86" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="O12" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P12" s="168" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="Q12" s="169" t="n">
-        <x:v>0.098</x:v>
-      </x:c>
-      <x:c r="R12" s="170" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); ABS ESD cover (5 g)</x:v>
-      </x:c>
-      <x:c r="S12" s="170" t="str">
-        <x:v>ACT_FR_UpperLeg + Upper_Leg + Upper_Leg_Cover</x:v>
-      </x:c>
-      <x:c r="T12" s="170" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="U12" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V12" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W12" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D12" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H12" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O12" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P12" s="306" t="n">
+        <x:v>172.5</x:v>
+      </x:c>
+      <x:c r="Q12" s="306" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="R12" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S12" s="301" t="str">
+        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T12" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U12" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V12" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W12" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="19" customHeight="1">
-      <x:c r="A13" s="43" t="str">
+      <x:c r="A13" s="359" t="str">
         <x:v>rf_lower_leg_link</x:v>
       </x:c>
-      <x:c r="B13" s="43" t="str">
+      <x:c r="B13" s="359" t="str">
         <x:v>meshes/rf_lower_leg_link.stl</x:v>
       </x:c>
-      <x:c r="C13" s="43" t="str">
+      <x:c r="C13" s="359" t="str">
         <x:v>meshes/rf_lower_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D13" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I13" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K13" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L13" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O13" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P13" s="168" t="n">
-        <x:v>114.5</x:v>
-      </x:c>
-      <x:c r="Q13" s="169" t="n">
-        <x:v>0.1145</x:v>
-      </x:c>
-      <x:c r="R13" s="170" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (53.5 g)</x:v>
-      </x:c>
-      <x:c r="S13" s="170" t="str">
-        <x:v>ACT_FR_LowerLeg + Lower_Leg_R</x:v>
-      </x:c>
-      <x:c r="T13" s="170" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="U13" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V13" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W13" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D13" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" s="306" t="n">
+        <x:v>59.5</x:v>
+      </x:c>
+      <x:c r="Q13" s="306" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="R13" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S13" s="301" t="str">
+        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T13" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U13" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V13" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W13" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="19" customHeight="1">
-      <x:c r="A14" s="43" t="str">
+      <x:c r="A14" s="359" t="str">
         <x:v>rf_foot_link</x:v>
       </x:c>
-      <x:c r="B14" s="43" t="str">
+      <x:c r="B14" s="359" t="str">
         <x:v>meshes/rf_foot_link.stl</x:v>
       </x:c>
-      <x:c r="C14" s="43" t="str">
+      <x:c r="C14" s="359" t="str">
         <x:v>meshes/rf_foot_link.stl</x:v>
       </x:c>
-      <x:c r="D14" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E14" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F14" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H14" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I14" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J14" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K14" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L14" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M14" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O14" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P14" s="168" t="n">
-        <x:v>6.5</x:v>
-      </x:c>
-      <x:c r="Q14" s="169" t="n">
-        <x:v>0.0065</x:v>
-      </x:c>
-      <x:c r="R14" s="170" t="str">
-        <x:v>TPU 95A (6.5 g)</x:v>
-      </x:c>
-      <x:c r="S14" s="170" t="str">
-        <x:v>Rubber_Foot FR</x:v>
-      </x:c>
-      <x:c r="T14" s="170" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="U14" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V14" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W14" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D14" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I14" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N14" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O14" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" s="306" t="n">
+        <x:v>17.5</x:v>
+      </x:c>
+      <x:c r="Q14" s="306" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="R14" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S14" s="301" t="str">
+        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T14" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U14" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V14" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W14" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="19" customHeight="1">
-      <x:c r="A15" s="43" t="str">
+      <x:c r="A15" s="359" t="str">
         <x:v>rh_hip_link</x:v>
       </x:c>
-      <x:c r="B15" s="43" t="str">
+      <x:c r="B15" s="359" t="str">
         <x:v>meshes/rh_hip_link.stl</x:v>
       </x:c>
-      <x:c r="C15" s="43" t="str">
+      <x:c r="C15" s="359" t="str">
         <x:v>meshes/rh_hip_link.stl</x:v>
       </x:c>
-      <x:c r="D15" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E15" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I15" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L15" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M15" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O15" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P15" s="168" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Q15" s="169" t="n">
-        <x:v>0.097</x:v>
-      </x:c>
-      <x:c r="R15" s="170" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); Steel fasteners (4 g)</x:v>
-      </x:c>
-      <x:c r="S15" s="170" t="str">
-        <x:v>ACT_RR_Shoulder + Shoulder_Joint_R + leg fasteners</x:v>
-      </x:c>
-      <x:c r="T15" s="170" t="str">
-        <x:v>4 g leg fasteners provisionally allocated to hip_link</x:v>
-      </x:c>
-      <x:c r="U15" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V15" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W15" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D15" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" s="306" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q15" s="306" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="R15" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S15" s="301" t="str">
+        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T15" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U15" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V15" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W15" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="19" customHeight="1">
-      <x:c r="A16" s="82" t="str">
+      <x:c r="A16" s="362" t="str">
         <x:v>rh_upper_leg_link</x:v>
       </x:c>
-      <x:c r="B16" s="82" t="str">
+      <x:c r="B16" s="362" t="str">
         <x:v>meshes/rh_upper_leg_link.stl</x:v>
       </x:c>
-      <x:c r="C16" s="82" t="str">
+      <x:c r="C16" s="362" t="str">
         <x:v>meshes/rh_upper_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D16" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E16" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F16" s="84" t="n">
-        <x:v>-0.09</x:v>
-      </x:c>
-      <x:c r="G16" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="86" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="I16" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J16" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L16" s="84" t="n">
-        <x:v>-0.09</x:v>
-      </x:c>
-      <x:c r="M16" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="86" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="O16" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P16" s="168" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="Q16" s="169" t="n">
-        <x:v>0.098</x:v>
-      </x:c>
-      <x:c r="R16" s="170" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); ABS ESD cover (5 g)</x:v>
-      </x:c>
-      <x:c r="S16" s="170" t="str">
-        <x:v>ACT_RR_UpperLeg + Upper_Leg + Upper_Leg_Cover</x:v>
-      </x:c>
-      <x:c r="T16" s="170" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="U16" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V16" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W16" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D16" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P16" s="306" t="n">
+        <x:v>172.5</x:v>
+      </x:c>
+      <x:c r="Q16" s="306" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="R16" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S16" s="301" t="str">
+        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T16" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U16" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V16" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W16" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="19" customHeight="1">
-      <x:c r="A17" s="43" t="str">
+      <x:c r="A17" s="359" t="str">
         <x:v>rh_lower_leg_link</x:v>
       </x:c>
-      <x:c r="B17" s="43" t="str">
+      <x:c r="B17" s="359" t="str">
         <x:v>meshes/rh_lower_leg_link.stl</x:v>
       </x:c>
-      <x:c r="C17" s="43" t="str">
+      <x:c r="C17" s="359" t="str">
         <x:v>meshes/rh_lower_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D17" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F17" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I17" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K17" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L17" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M17" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O17" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P17" s="168" t="n">
-        <x:v>114.5</x:v>
-      </x:c>
-      <x:c r="Q17" s="169" t="n">
-        <x:v>0.1145</x:v>
-      </x:c>
-      <x:c r="R17" s="170" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (53.5 g)</x:v>
-      </x:c>
-      <x:c r="S17" s="170" t="str">
-        <x:v>ACT_RR_LowerLeg + Lower_Leg_R</x:v>
-      </x:c>
-      <x:c r="T17" s="170" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="U17" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V17" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W17" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D17" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P17" s="306" t="n">
+        <x:v>59.5</x:v>
+      </x:c>
+      <x:c r="Q17" s="306" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="R17" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S17" s="301" t="str">
+        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T17" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U17" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V17" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W17" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="19" customHeight="1">
-      <x:c r="A18" s="43" t="str">
+      <x:c r="A18" s="359" t="str">
         <x:v>rh_foot_link</x:v>
       </x:c>
-      <x:c r="B18" s="43" t="str">
+      <x:c r="B18" s="359" t="str">
         <x:v>meshes/rh_foot_link.stl</x:v>
       </x:c>
-      <x:c r="C18" s="43" t="str">
+      <x:c r="C18" s="359" t="str">
         <x:v>meshes/rh_foot_link.stl</x:v>
       </x:c>
-      <x:c r="D18" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E18" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F18" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H18" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I18" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J18" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K18" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L18" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M18" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O18" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P18" s="168" t="n">
-        <x:v>6.5</x:v>
-      </x:c>
-      <x:c r="Q18" s="169" t="n">
-        <x:v>0.0065</x:v>
-      </x:c>
-      <x:c r="R18" s="170" t="str">
-        <x:v>TPU 95A (6.5 g)</x:v>
-      </x:c>
-      <x:c r="S18" s="170" t="str">
-        <x:v>Rubber_Foot RR</x:v>
-      </x:c>
-      <x:c r="T18" s="170" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="U18" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V18" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W18" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D18" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G18" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P18" s="306" t="n">
+        <x:v>17.5</x:v>
+      </x:c>
+      <x:c r="Q18" s="306" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="R18" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S18" s="301" t="str">
+        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T18" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U18" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V18" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W18" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="19" customHeight="1">
-      <x:c r="A19" s="43" t="str">
+      <x:c r="A19" s="359" t="str">
         <x:v>lh_hip_link</x:v>
       </x:c>
-      <x:c r="B19" s="43" t="str">
+      <x:c r="B19" s="359" t="str">
         <x:v>meshes/lh_hip_link.stl</x:v>
       </x:c>
-      <x:c r="C19" s="43" t="str">
+      <x:c r="C19" s="359" t="str">
         <x:v>meshes/lh_hip_link.stl</x:v>
       </x:c>
-      <x:c r="D19" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E19" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F19" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I19" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J19" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K19" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L19" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M19" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O19" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P19" s="168" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Q19" s="169" t="n">
-        <x:v>0.097</x:v>
-      </x:c>
-      <x:c r="R19" s="170" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); Steel fasteners (4 g)</x:v>
-      </x:c>
-      <x:c r="S19" s="170" t="str">
-        <x:v>ACT_RL_Shoulder + Shoulder_Joint_L + leg fasteners</x:v>
-      </x:c>
-      <x:c r="T19" s="170" t="str">
-        <x:v>4 g leg fasteners provisionally allocated to hip_link</x:v>
-      </x:c>
-      <x:c r="U19" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V19" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W19" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D19" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L19" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O19" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P19" s="306" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q19" s="306" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="R19" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S19" s="301" t="str">
+        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T19" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U19" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V19" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W19" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="19" customHeight="1">
-      <x:c r="A20" s="82" t="str">
+      <x:c r="A20" s="362" t="str">
         <x:v>lh_upper_leg_link</x:v>
       </x:c>
-      <x:c r="B20" s="82" t="str">
+      <x:c r="B20" s="362" t="str">
         <x:v>meshes/lh_upper_leg_link.stl</x:v>
       </x:c>
-      <x:c r="C20" s="82" t="str">
+      <x:c r="C20" s="362" t="str">
         <x:v>meshes/lh_upper_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D20" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E20" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F20" s="84" t="n">
-        <x:v>-0.09</x:v>
-      </x:c>
-      <x:c r="G20" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H20" s="86" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="I20" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J20" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K20" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L20" s="84" t="n">
-        <x:v>-0.09</x:v>
-      </x:c>
-      <x:c r="M20" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="86" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="O20" s="86" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P20" s="168" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="Q20" s="169" t="n">
-        <x:v>0.098</x:v>
-      </x:c>
-      <x:c r="R20" s="170" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); ABS ESD cover (5 g)</x:v>
-      </x:c>
-      <x:c r="S20" s="170" t="str">
-        <x:v>ACT_RL_UpperLeg + Upper_Leg + Upper_Leg_Cover</x:v>
-      </x:c>
-      <x:c r="T20" s="170" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="U20" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V20" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W20" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D20" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F20" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H20" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I20" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J20" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K20" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L20" s="363" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N20" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O20" s="364" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P20" s="306" t="n">
+        <x:v>172.5</x:v>
+      </x:c>
+      <x:c r="Q20" s="306" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="R20" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S20" s="301" t="str">
+        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T20" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U20" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V20" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W20" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="19" customHeight="1">
-      <x:c r="A21" s="43" t="str">
+      <x:c r="A21" s="359" t="str">
         <x:v>lh_lower_leg_link</x:v>
       </x:c>
-      <x:c r="B21" s="43" t="str">
+      <x:c r="B21" s="359" t="str">
         <x:v>meshes/lh_lower_leg_link.stl</x:v>
       </x:c>
-      <x:c r="C21" s="43" t="str">
+      <x:c r="C21" s="359" t="str">
         <x:v>meshes/lh_lower_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D21" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E21" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F21" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H21" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I21" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J21" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K21" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L21" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M21" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O21" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P21" s="168" t="n">
-        <x:v>114.5</x:v>
-      </x:c>
-      <x:c r="Q21" s="169" t="n">
-        <x:v>0.1145</x:v>
-      </x:c>
-      <x:c r="R21" s="170" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (53.5 g)</x:v>
-      </x:c>
-      <x:c r="S21" s="170" t="str">
-        <x:v>ACT_RL_LowerLeg + Lower_Leg_L</x:v>
-      </x:c>
-      <x:c r="T21" s="170" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="U21" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V21" s="170" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W21" s="171" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D21" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I21" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J21" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K21" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L21" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N21" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O21" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P21" s="306" t="n">
+        <x:v>59.5</x:v>
+      </x:c>
+      <x:c r="Q21" s="306" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="R21" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S21" s="301" t="str">
+        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T21" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U21" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V21" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W21" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="19" customHeight="1">
-      <x:c r="A22" s="43" t="str">
+      <x:c r="A22" s="359" t="str">
         <x:v>lh_foot_link</x:v>
       </x:c>
-      <x:c r="B22" s="43" t="str">
+      <x:c r="B22" s="359" t="str">
         <x:v>meshes/lh_foot_link.stl</x:v>
       </x:c>
-      <x:c r="C22" s="43" t="str">
+      <x:c r="C22" s="359" t="str">
         <x:v>meshes/lh_foot_link.stl</x:v>
       </x:c>
-      <x:c r="D22" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E22" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F22" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H22" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I22" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J22" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K22" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L22" s="70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M22" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O22" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P22" s="172" t="n">
-        <x:v>6.5</x:v>
-      </x:c>
-      <x:c r="Q22" s="173" t="n">
-        <x:v>0.0065</x:v>
-      </x:c>
-      <x:c r="R22" s="174" t="str">
-        <x:v>TPU 95A (6.5 g)</x:v>
-      </x:c>
-      <x:c r="S22" s="174" t="str">
-        <x:v>Rubber_Foot RL</x:v>
-      </x:c>
-      <x:c r="T22" s="174" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="U22" s="174" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="V22" s="174" t="str">
-        <x:v>Pending CAD</x:v>
-      </x:c>
-      <x:c r="W22" s="175" t="str">
-        <x:v>Comment only; inertial block deferred</x:v>
+      <x:c r="D22" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E22" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F22" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G22" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H22" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J22" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K22" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L22" s="360" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M22" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N22" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O22" s="361" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P22" s="306" t="n">
+        <x:v>17.5</x:v>
+      </x:c>
+      <x:c r="Q22" s="306" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="R22" s="301" t="str">
+        <x:v>CAD physical-property report</x:v>
+      </x:c>
+      <x:c r="S22" s="301" t="str">
+        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="T22" s="301" t="str">
+        <x:v>CoM available</x:v>
+      </x:c>
+      <x:c r="U22" s="301" t="str">
+        <x:v>Tensor available</x:v>
+      </x:c>
+      <x:c r="V22" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; inserted</x:v>
+      </x:c>
+      <x:c r="W22" s="301" t="str">
+        <x:v>Simulation-ready</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4047,7 +4892,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfed9257a10834829"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94ad51e75eba4da9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4056,9 +4901,9 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="75" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="29" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="105" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
@@ -4283,10 +5128,10 @@
         <x:v>✓</x:v>
       </x:c>
       <x:c r="B20" s="82" t="str">
-        <x:v>upper_leg_link (×4)</x:v>
+        <x:v>Mesh origins (tutti i link)</x:v>
       </x:c>
       <x:c r="C20" s="115" t="str">
-        <x:v>Mesh visual + collision: xyz = 0, 0, -0.090 m · rpy = 0°, 180°, 0°. Forma equivalente minima del doppio ribaltamento verificato.</x:v>
+        <x:v>Visual + collision: xyz = 0, 0, 0 m · rpy = 0°, 0°, 0°.</x:v>
       </x:c>
       <x:c r="D20" s="115"/>
       <x:c r="E20" s="115"/>
@@ -4310,55 +5155,66 @@
       <x:c r="G21" s="115"/>
       <x:c r="H21" s="115"/>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="382" t="str">
+        <x:v>Proprietà dinamiche REV00</x:v>
+      </x:c>
+      <x:c r="B22" s="382"/>
+      <x:c r="C22" s="382"/>
+    </x:row>
     <x:row r="23" ht="20" customHeight="1">
-      <x:c r="A23" s="245" t="str">
-        <x:v>Proprietà fisiche REV00</x:v>
-      </x:c>
-      <x:c r="B23" s="246"/>
-      <x:c r="C23" s="247"/>
+      <x:c r="A23" s="383" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B23" s="383" t="str">
+        <x:v>Masse per link</x:v>
+      </x:c>
+      <x:c r="C23" s="383" t="str">
+        <x:v>Masse CAD riconciliate: totale 17-link = 2.480 kg. Vedi Mass_Reconciliation.</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="34" customHeight="1">
-      <x:c r="A24" s="250" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B24" s="162" t="str">
-        <x:v>Masse per link</x:v>
-      </x:c>
-      <x:c r="C24" s="163" t="str">
-        <x:v>Masse reali inserite nel foglio Link_Engineering e riportate in Mesh_Transforms. Totale URDF REV00: 1.549 kg.</x:v>
+      <x:c r="A24" s="384" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B24" s="301" t="str">
+        <x:v>Centro di massa</x:v>
+      </x:c>
+      <x:c r="C24" s="301" t="str">
+        <x:v>CoM per-link importati dal CAD in metri, espressi nel frame locale URDF.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="34" customHeight="1">
-      <x:c r="A25" s="250" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B25" s="162" t="str">
-        <x:v>Materiali</x:v>
-      </x:c>
-      <x:c r="C25" s="163" t="str">
-        <x:v>Composizione ingegneristica documentata per ogni link. Il materiale URDF standard è solo visivo; la composizione fisica è annotata nel file URDF come metadata commentata.</x:v>
+      <x:c r="A25" s="384" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B25" s="301" t="str">
+        <x:v>Inerzia</x:v>
+      </x:c>
+      <x:c r="C25" s="301" t="str">
+        <x:v>Tensori al CoM ricostruiti da assi principali + raggi di girazione CAD e inseriti come blocchi &lt;inertial&gt;.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="250" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B26" s="162" t="str">
-        <x:v>Inertial</x:v>
-      </x:c>
-      <x:c r="C26" s="163" t="str">
-        <x:v>Blocco &lt;inertial&gt; non ancora scritto: per una simulazione dinamica corretta servono baricentro e tensore d’inerzia estratti dal CAD.</x:v>
+      <x:c r="A26" s="384" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B26" s="301" t="str">
+        <x:v>Validazione</x:v>
+      </x:c>
+      <x:c r="C26" s="301" t="str">
+        <x:v>Somma 17 link: massa uguale all’assieme CAD; errore massimo CoM 0.374 mm rispetto al report assembly.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="34" customHeight="1">
-      <x:c r="A27" s="251" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B27" s="166" t="str">
-        <x:v>Hardware fuori modello</x:v>
-      </x:c>
-      <x:c r="C27" s="167" t="str">
-        <x:v>Il motore yaw testa da 61 g è presente in Engineering_Data ma non fa parte dell’URDF REV00 a 17 link.</x:v>
+      <x:c r="A27" s="384" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B27" s="301" t="str">
+        <x:v>Neck yaw actuator</x:v>
+      </x:c>
+      <x:c r="C27" s="301" t="str">
+        <x:v>Nessun link separato in REV00: non è stato aggiunto senza un report CAD della sua posa montata.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4387,677 +5243,677 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="54" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="44" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="34" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="31" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="31" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="46" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="52" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="36" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="139" t="str">
+      <x:c r="A1" s="289" t="str">
         <x:v>MATDOG — Proprietà fisiche per link URDF</x:v>
       </x:c>
-      <x:c r="B1" s="139"/>
-      <x:c r="C1" s="139"/>
-      <x:c r="D1" s="139"/>
-      <x:c r="E1" s="139"/>
-      <x:c r="F1" s="139"/>
-      <x:c r="G1" s="139"/>
-      <x:c r="H1" s="139"/>
-      <x:c r="I1" s="139"/>
-      <x:c r="J1" s="139"/>
-      <x:c r="K1" s="139"/>
-    </x:row>
-    <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="144" t="str">
-        <x:v>Masse da Engineering_Data.xlsx / Weight. Ogni valore è assegnato al link URDF che rappresenta l’assieme CAD corrispondente. Le proprietà inerziali non sono ancora finali: richiedono baricentro e tensore dal CAD.</x:v>
-      </x:c>
-      <x:c r="B2" s="144"/>
-      <x:c r="C2" s="144"/>
-      <x:c r="D2" s="144"/>
-      <x:c r="E2" s="144"/>
-      <x:c r="F2" s="144"/>
-      <x:c r="G2" s="144"/>
-      <x:c r="H2" s="144"/>
-      <x:c r="I2" s="144"/>
-      <x:c r="J2" s="144"/>
-      <x:c r="K2" s="144"/>
+      <x:c r="B1" s="289"/>
+      <x:c r="C1" s="289"/>
+      <x:c r="D1" s="289"/>
+      <x:c r="E1" s="289"/>
+      <x:c r="F1" s="289"/>
+      <x:c r="G1" s="289"/>
+      <x:c r="H1" s="289"/>
+      <x:c r="I1" s="289"/>
+      <x:c r="J1" s="289"/>
+      <x:c r="K1" s="289"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="294" t="str">
+        <x:v>Masse, CoM e inerzie dinamiche sono ora definite dal CAD. Il foglio Inertial_Properties è la sorgente canonica dei valori URDF; Engineering_Weight_Source resta un confronto storico.</x:v>
+      </x:c>
+      <x:c r="B2" s="294"/>
+      <x:c r="C2" s="294"/>
+      <x:c r="D2" s="294"/>
+      <x:c r="E2" s="294"/>
+      <x:c r="F2" s="294"/>
+      <x:c r="G2" s="294"/>
+      <x:c r="H2" s="294"/>
+      <x:c r="I2" s="294"/>
+      <x:c r="J2" s="294"/>
+      <x:c r="K2" s="294"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="157" t="str">
+      <x:c r="A4" s="345" t="str">
         <x:v>Link</x:v>
       </x:c>
-      <x:c r="B4" s="158" t="str">
+      <x:c r="B4" s="345" t="str">
         <x:v>Zone</x:v>
       </x:c>
-      <x:c r="C4" s="158" t="str">
+      <x:c r="C4" s="345" t="str">
         <x:v>URDF mesh</x:v>
       </x:c>
-      <x:c r="D4" s="158" t="str">
+      <x:c r="D4" s="345" t="str">
         <x:v>Mass [g]</x:v>
       </x:c>
-      <x:c r="E4" s="158" t="str">
+      <x:c r="E4" s="345" t="str">
         <x:v>Mass [kg]</x:v>
       </x:c>
-      <x:c r="F4" s="158" t="str">
+      <x:c r="F4" s="345" t="str">
         <x:v>Assembly grouping</x:v>
       </x:c>
-      <x:c r="G4" s="158" t="str">
+      <x:c r="G4" s="345" t="str">
         <x:v>Material composition</x:v>
       </x:c>
-      <x:c r="H4" s="158" t="str">
+      <x:c r="H4" s="345" t="str">
         <x:v>Components from Engineering_Data</x:v>
       </x:c>
-      <x:c r="I4" s="158" t="str">
+      <x:c r="I4" s="345" t="str">
         <x:v>Fastener allocation</x:v>
       </x:c>
-      <x:c r="J4" s="158" t="str">
+      <x:c r="J4" s="345" t="str">
         <x:v>Inertial status</x:v>
       </x:c>
-      <x:c r="K4" s="159" t="str">
+      <x:c r="K4" s="345" t="str">
         <x:v>URDF status</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="203" t="str">
+      <x:c r="A5" s="328" t="str">
         <x:v>base_link</x:v>
       </x:c>
-      <x:c r="B5" s="204" t="str">
+      <x:c r="B5" s="328" t="str">
         <x:v>Body</x:v>
       </x:c>
-      <x:c r="C5" s="204" t="str">
+      <x:c r="C5" s="328" t="str">
         <x:v>meshes/base_link.stl</x:v>
       </x:c>
-      <x:c r="D5" s="205" t="n">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="E5" s="206" t="n">
-        <x:v>0.285</x:v>
-      </x:c>
-      <x:c r="F5" s="204" t="str">
-        <x:v>Lower chassis assembly</x:v>
-      </x:c>
-      <x:c r="G5" s="204" t="str">
-        <x:v>PPA+CF (283 g); Steel fasteners (2 g)</x:v>
-      </x:c>
-      <x:c r="H5" s="204" t="str">
-        <x:v>Lower_Chassis 283 g + Fasteners 2 g</x:v>
-      </x:c>
-      <x:c r="I5" s="204" t="str">
-        <x:v>2 g assigned directly to base_link</x:v>
-      </x:c>
-      <x:c r="J5" s="204" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K5" s="207" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D5" s="329" t="n">
+        <x:v>1282</x:v>
+      </x:c>
+      <x:c r="E5" s="329" t="n">
+        <x:v>1.282</x:v>
+      </x:c>
+      <x:c r="F5" s="328" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G5" s="328" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H5" s="328" t="str">
+        <x:v>physprop__base_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I5" s="328" t="str">
+        <x:v>Direct CAD</x:v>
+      </x:c>
+      <x:c r="J5" s="328" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K5" s="328" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="208" t="str">
+      <x:c r="A6" s="331" t="str">
         <x:v>lf_hip_link</x:v>
       </x:c>
-      <x:c r="B6" s="209" t="str">
+      <x:c r="B6" s="331" t="str">
         <x:v>LF</x:v>
       </x:c>
-      <x:c r="C6" s="209" t="str">
+      <x:c r="C6" s="331" t="str">
         <x:v>meshes/lf_hip_link.stl</x:v>
       </x:c>
-      <x:c r="D6" s="210" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E6" s="211" t="n">
-        <x:v>0.097</x:v>
-      </x:c>
-      <x:c r="F6" s="209" t="str">
-        <x:v>Hip / shoulder assembly</x:v>
-      </x:c>
-      <x:c r="G6" s="209" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); Steel fasteners (4 g)</x:v>
-      </x:c>
-      <x:c r="H6" s="209" t="str">
-        <x:v>ACT_FL_Shoulder + Shoulder_Joint_L + leg fasteners</x:v>
-      </x:c>
-      <x:c r="I6" s="209" t="str">
-        <x:v>4 g leg fasteners provisionally allocated to hip_link</x:v>
-      </x:c>
-      <x:c r="J6" s="209" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K6" s="212" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D6" s="332" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E6" s="332" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="F6" s="331" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G6" s="331" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H6" s="331" t="str">
+        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I6" s="331" t="str">
+        <x:v>Direct CAD</x:v>
+      </x:c>
+      <x:c r="J6" s="331" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K6" s="331" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="213" t="str">
+      <x:c r="A7" s="334" t="str">
         <x:v>lf_upper_leg_link</x:v>
       </x:c>
-      <x:c r="B7" s="214" t="str">
+      <x:c r="B7" s="334" t="str">
         <x:v>LF</x:v>
       </x:c>
-      <x:c r="C7" s="214" t="str">
+      <x:c r="C7" s="334" t="str">
         <x:v>meshes/lf_upper_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D7" s="215" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="E7" s="216" t="n">
-        <x:v>0.098</x:v>
-      </x:c>
-      <x:c r="F7" s="214" t="str">
-        <x:v>Upper-leg assembly</x:v>
-      </x:c>
-      <x:c r="G7" s="214" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); ABS ESD cover (5 g)</x:v>
-      </x:c>
-      <x:c r="H7" s="214" t="str">
-        <x:v>ACT_FL_UpperLeg + Upper_Leg + Upper_Leg_Cover</x:v>
-      </x:c>
-      <x:c r="I7" s="214" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="J7" s="214" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K7" s="217" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D7" s="335" t="n">
+        <x:v>172.5</x:v>
+      </x:c>
+      <x:c r="E7" s="335" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="F7" s="334" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G7" s="334" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H7" s="334" t="str">
+        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I7" s="334" t="str">
+        <x:v>Direct CAD</x:v>
+      </x:c>
+      <x:c r="J7" s="334" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K7" s="334" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="218" t="str">
+      <x:c r="A8" s="337" t="str">
         <x:v>lf_lower_leg_link</x:v>
       </x:c>
-      <x:c r="B8" s="219" t="str">
+      <x:c r="B8" s="337" t="str">
         <x:v>LF</x:v>
       </x:c>
-      <x:c r="C8" s="219" t="str">
+      <x:c r="C8" s="337" t="str">
         <x:v>meshes/lf_lower_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D8" s="220" t="n">
-        <x:v>114.5</x:v>
-      </x:c>
-      <x:c r="E8" s="221" t="n">
-        <x:v>0.1145</x:v>
-      </x:c>
-      <x:c r="F8" s="219" t="str">
-        <x:v>Lower-leg assembly</x:v>
-      </x:c>
-      <x:c r="G8" s="219" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (53.5 g)</x:v>
-      </x:c>
-      <x:c r="H8" s="219" t="str">
-        <x:v>ACT_FL_LowerLeg + Lower_Leg_L</x:v>
-      </x:c>
-      <x:c r="I8" s="219" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="J8" s="219" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K8" s="222" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D8" s="338" t="n">
+        <x:v>59.5</x:v>
+      </x:c>
+      <x:c r="E8" s="338" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="F8" s="337" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G8" s="337" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H8" s="337" t="str">
+        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I8" s="337" t="str">
+        <x:v>Direct CAD</x:v>
+      </x:c>
+      <x:c r="J8" s="337" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K8" s="337" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="223" t="str">
+      <x:c r="A9" s="340" t="str">
         <x:v>lf_foot_link</x:v>
       </x:c>
-      <x:c r="B9" s="224" t="str">
+      <x:c r="B9" s="340" t="str">
         <x:v>LF</x:v>
       </x:c>
-      <x:c r="C9" s="224" t="str">
+      <x:c r="C9" s="340" t="str">
         <x:v>meshes/lf_foot_link.stl</x:v>
       </x:c>
-      <x:c r="D9" s="225" t="n">
-        <x:v>6.5</x:v>
-      </x:c>
-      <x:c r="E9" s="226" t="n">
-        <x:v>0.0065</x:v>
-      </x:c>
-      <x:c r="F9" s="224" t="str">
-        <x:v>Rubber foot</x:v>
-      </x:c>
-      <x:c r="G9" s="224" t="str">
-        <x:v>TPU 95A (6.5 g)</x:v>
-      </x:c>
-      <x:c r="H9" s="224" t="str">
-        <x:v>Rubber_Foot FL</x:v>
-      </x:c>
-      <x:c r="I9" s="224" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="J9" s="224" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K9" s="227" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D9" s="341" t="n">
+        <x:v>17.5</x:v>
+      </x:c>
+      <x:c r="E9" s="341" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="F9" s="340" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G9" s="340" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H9" s="340" t="str">
+        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I9" s="340" t="str">
+        <x:v>Direct CAD</x:v>
+      </x:c>
+      <x:c r="J9" s="340" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K9" s="340" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="208" t="str">
+      <x:c r="A10" s="331" t="str">
         <x:v>rf_hip_link</x:v>
       </x:c>
-      <x:c r="B10" s="209" t="str">
+      <x:c r="B10" s="331" t="str">
         <x:v>RF</x:v>
       </x:c>
-      <x:c r="C10" s="209" t="str">
+      <x:c r="C10" s="331" t="str">
         <x:v>meshes/rf_hip_link.stl</x:v>
       </x:c>
-      <x:c r="D10" s="210" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E10" s="211" t="n">
-        <x:v>0.097</x:v>
-      </x:c>
-      <x:c r="F10" s="209" t="str">
-        <x:v>Hip / shoulder assembly</x:v>
-      </x:c>
-      <x:c r="G10" s="209" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); Steel fasteners (4 g)</x:v>
-      </x:c>
-      <x:c r="H10" s="209" t="str">
-        <x:v>ACT_FR_Shoulder + Shoulder_Joint_R + leg fasteners</x:v>
-      </x:c>
-      <x:c r="I10" s="209" t="str">
-        <x:v>4 g leg fasteners provisionally allocated to hip_link</x:v>
-      </x:c>
-      <x:c r="J10" s="209" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K10" s="212" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D10" s="332" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E10" s="332" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="F10" s="331" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G10" s="331" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H10" s="331" t="str">
+        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I10" s="331" t="str">
+        <x:v>LF symmetry-derived</x:v>
+      </x:c>
+      <x:c r="J10" s="331" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K10" s="331" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="213" t="str">
+      <x:c r="A11" s="334" t="str">
         <x:v>rf_upper_leg_link</x:v>
       </x:c>
-      <x:c r="B11" s="214" t="str">
+      <x:c r="B11" s="334" t="str">
         <x:v>RF</x:v>
       </x:c>
-      <x:c r="C11" s="214" t="str">
+      <x:c r="C11" s="334" t="str">
         <x:v>meshes/rf_upper_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D11" s="215" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="E11" s="216" t="n">
-        <x:v>0.098</x:v>
-      </x:c>
-      <x:c r="F11" s="214" t="str">
-        <x:v>Upper-leg assembly</x:v>
-      </x:c>
-      <x:c r="G11" s="214" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); ABS ESD cover (5 g)</x:v>
-      </x:c>
-      <x:c r="H11" s="214" t="str">
-        <x:v>ACT_FR_UpperLeg + Upper_Leg + Upper_Leg_Cover</x:v>
-      </x:c>
-      <x:c r="I11" s="214" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="J11" s="214" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K11" s="217" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D11" s="335" t="n">
+        <x:v>172.5</x:v>
+      </x:c>
+      <x:c r="E11" s="335" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="F11" s="334" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G11" s="334" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H11" s="334" t="str">
+        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I11" s="334" t="str">
+        <x:v>LF symmetry-derived</x:v>
+      </x:c>
+      <x:c r="J11" s="334" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K11" s="334" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="218" t="str">
+      <x:c r="A12" s="337" t="str">
         <x:v>rf_lower_leg_link</x:v>
       </x:c>
-      <x:c r="B12" s="219" t="str">
+      <x:c r="B12" s="337" t="str">
         <x:v>RF</x:v>
       </x:c>
-      <x:c r="C12" s="219" t="str">
+      <x:c r="C12" s="337" t="str">
         <x:v>meshes/rf_lower_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D12" s="220" t="n">
-        <x:v>114.5</x:v>
-      </x:c>
-      <x:c r="E12" s="221" t="n">
-        <x:v>0.1145</x:v>
-      </x:c>
-      <x:c r="F12" s="219" t="str">
-        <x:v>Lower-leg assembly</x:v>
-      </x:c>
-      <x:c r="G12" s="219" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (53.5 g)</x:v>
-      </x:c>
-      <x:c r="H12" s="219" t="str">
-        <x:v>ACT_FR_LowerLeg + Lower_Leg_R</x:v>
-      </x:c>
-      <x:c r="I12" s="219" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="J12" s="219" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K12" s="222" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D12" s="338" t="n">
+        <x:v>59.5</x:v>
+      </x:c>
+      <x:c r="E12" s="338" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="F12" s="337" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G12" s="337" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H12" s="337" t="str">
+        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I12" s="337" t="str">
+        <x:v>LF symmetry-derived</x:v>
+      </x:c>
+      <x:c r="J12" s="337" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K12" s="337" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="223" t="str">
+      <x:c r="A13" s="340" t="str">
         <x:v>rf_foot_link</x:v>
       </x:c>
-      <x:c r="B13" s="224" t="str">
+      <x:c r="B13" s="340" t="str">
         <x:v>RF</x:v>
       </x:c>
-      <x:c r="C13" s="224" t="str">
+      <x:c r="C13" s="340" t="str">
         <x:v>meshes/rf_foot_link.stl</x:v>
       </x:c>
-      <x:c r="D13" s="225" t="n">
-        <x:v>6.5</x:v>
-      </x:c>
-      <x:c r="E13" s="226" t="n">
-        <x:v>0.0065</x:v>
-      </x:c>
-      <x:c r="F13" s="224" t="str">
-        <x:v>Rubber foot</x:v>
-      </x:c>
-      <x:c r="G13" s="224" t="str">
-        <x:v>TPU 95A (6.5 g)</x:v>
-      </x:c>
-      <x:c r="H13" s="224" t="str">
-        <x:v>Rubber_Foot FR</x:v>
-      </x:c>
-      <x:c r="I13" s="224" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="J13" s="224" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K13" s="227" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D13" s="341" t="n">
+        <x:v>17.5</x:v>
+      </x:c>
+      <x:c r="E13" s="341" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="F13" s="340" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G13" s="340" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H13" s="340" t="str">
+        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I13" s="340" t="str">
+        <x:v>LF symmetry-derived</x:v>
+      </x:c>
+      <x:c r="J13" s="340" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K13" s="340" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="208" t="str">
+      <x:c r="A14" s="331" t="str">
         <x:v>rh_hip_link</x:v>
       </x:c>
-      <x:c r="B14" s="209" t="str">
+      <x:c r="B14" s="331" t="str">
         <x:v>RH</x:v>
       </x:c>
-      <x:c r="C14" s="209" t="str">
+      <x:c r="C14" s="331" t="str">
         <x:v>meshes/rh_hip_link.stl</x:v>
       </x:c>
-      <x:c r="D14" s="210" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E14" s="211" t="n">
-        <x:v>0.097</x:v>
-      </x:c>
-      <x:c r="F14" s="209" t="str">
-        <x:v>Hip / shoulder assembly</x:v>
-      </x:c>
-      <x:c r="G14" s="209" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); Steel fasteners (4 g)</x:v>
-      </x:c>
-      <x:c r="H14" s="209" t="str">
-        <x:v>ACT_RR_Shoulder + Shoulder_Joint_R + leg fasteners</x:v>
-      </x:c>
-      <x:c r="I14" s="209" t="str">
-        <x:v>4 g leg fasteners provisionally allocated to hip_link</x:v>
-      </x:c>
-      <x:c r="J14" s="209" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K14" s="212" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D14" s="332" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E14" s="332" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="F14" s="331" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G14" s="331" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H14" s="331" t="str">
+        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I14" s="331" t="str">
+        <x:v>LF symmetry-derived</x:v>
+      </x:c>
+      <x:c r="J14" s="331" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K14" s="331" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="213" t="str">
+      <x:c r="A15" s="334" t="str">
         <x:v>rh_upper_leg_link</x:v>
       </x:c>
-      <x:c r="B15" s="214" t="str">
+      <x:c r="B15" s="334" t="str">
         <x:v>RH</x:v>
       </x:c>
-      <x:c r="C15" s="214" t="str">
+      <x:c r="C15" s="334" t="str">
         <x:v>meshes/rh_upper_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D15" s="215" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="E15" s="216" t="n">
-        <x:v>0.098</x:v>
-      </x:c>
-      <x:c r="F15" s="214" t="str">
-        <x:v>Upper-leg assembly</x:v>
-      </x:c>
-      <x:c r="G15" s="214" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); ABS ESD cover (5 g)</x:v>
-      </x:c>
-      <x:c r="H15" s="214" t="str">
-        <x:v>ACT_RR_UpperLeg + Upper_Leg + Upper_Leg_Cover</x:v>
-      </x:c>
-      <x:c r="I15" s="214" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="J15" s="214" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K15" s="217" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D15" s="335" t="n">
+        <x:v>172.5</x:v>
+      </x:c>
+      <x:c r="E15" s="335" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="F15" s="334" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G15" s="334" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H15" s="334" t="str">
+        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I15" s="334" t="str">
+        <x:v>LF symmetry-derived</x:v>
+      </x:c>
+      <x:c r="J15" s="334" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K15" s="334" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="218" t="str">
+      <x:c r="A16" s="337" t="str">
         <x:v>rh_lower_leg_link</x:v>
       </x:c>
-      <x:c r="B16" s="219" t="str">
+      <x:c r="B16" s="337" t="str">
         <x:v>RH</x:v>
       </x:c>
-      <x:c r="C16" s="219" t="str">
+      <x:c r="C16" s="337" t="str">
         <x:v>meshes/rh_lower_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D16" s="220" t="n">
-        <x:v>114.5</x:v>
-      </x:c>
-      <x:c r="E16" s="221" t="n">
-        <x:v>0.1145</x:v>
-      </x:c>
-      <x:c r="F16" s="219" t="str">
-        <x:v>Lower-leg assembly</x:v>
-      </x:c>
-      <x:c r="G16" s="219" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (53.5 g)</x:v>
-      </x:c>
-      <x:c r="H16" s="219" t="str">
-        <x:v>ACT_RR_LowerLeg + Lower_Leg_R</x:v>
-      </x:c>
-      <x:c r="I16" s="219" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="J16" s="219" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K16" s="222" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D16" s="338" t="n">
+        <x:v>59.5</x:v>
+      </x:c>
+      <x:c r="E16" s="338" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="F16" s="337" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G16" s="337" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H16" s="337" t="str">
+        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I16" s="337" t="str">
+        <x:v>LF symmetry-derived</x:v>
+      </x:c>
+      <x:c r="J16" s="337" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K16" s="337" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="223" t="str">
+      <x:c r="A17" s="340" t="str">
         <x:v>rh_foot_link</x:v>
       </x:c>
-      <x:c r="B17" s="224" t="str">
+      <x:c r="B17" s="340" t="str">
         <x:v>RH</x:v>
       </x:c>
-      <x:c r="C17" s="224" t="str">
+      <x:c r="C17" s="340" t="str">
         <x:v>meshes/rh_foot_link.stl</x:v>
       </x:c>
-      <x:c r="D17" s="225" t="n">
-        <x:v>6.5</x:v>
-      </x:c>
-      <x:c r="E17" s="226" t="n">
-        <x:v>0.0065</x:v>
-      </x:c>
-      <x:c r="F17" s="224" t="str">
-        <x:v>Rubber foot</x:v>
-      </x:c>
-      <x:c r="G17" s="224" t="str">
-        <x:v>TPU 95A (6.5 g)</x:v>
-      </x:c>
-      <x:c r="H17" s="224" t="str">
-        <x:v>Rubber_Foot RR</x:v>
-      </x:c>
-      <x:c r="I17" s="224" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="J17" s="224" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K17" s="227" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D17" s="341" t="n">
+        <x:v>17.5</x:v>
+      </x:c>
+      <x:c r="E17" s="341" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="F17" s="340" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G17" s="340" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H17" s="340" t="str">
+        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I17" s="340" t="str">
+        <x:v>LF symmetry-derived</x:v>
+      </x:c>
+      <x:c r="J17" s="340" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K17" s="340" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="208" t="str">
+      <x:c r="A18" s="331" t="str">
         <x:v>lh_hip_link</x:v>
       </x:c>
-      <x:c r="B18" s="209" t="str">
+      <x:c r="B18" s="331" t="str">
         <x:v>LH</x:v>
       </x:c>
-      <x:c r="C18" s="209" t="str">
+      <x:c r="C18" s="331" t="str">
         <x:v>meshes/lh_hip_link.stl</x:v>
       </x:c>
-      <x:c r="D18" s="210" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E18" s="211" t="n">
-        <x:v>0.097</x:v>
-      </x:c>
-      <x:c r="F18" s="209" t="str">
-        <x:v>Hip / shoulder assembly</x:v>
-      </x:c>
-      <x:c r="G18" s="209" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); Steel fasteners (4 g)</x:v>
-      </x:c>
-      <x:c r="H18" s="209" t="str">
-        <x:v>ACT_RL_Shoulder + Shoulder_Joint_L + leg fasteners</x:v>
-      </x:c>
-      <x:c r="I18" s="209" t="str">
-        <x:v>4 g leg fasteners provisionally allocated to hip_link</x:v>
-      </x:c>
-      <x:c r="J18" s="209" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K18" s="212" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D18" s="332" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E18" s="332" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="F18" s="331" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G18" s="331" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H18" s="331" t="str">
+        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I18" s="331" t="str">
+        <x:v>LF symmetry-derived</x:v>
+      </x:c>
+      <x:c r="J18" s="331" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K18" s="331" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="213" t="str">
+      <x:c r="A19" s="334" t="str">
         <x:v>lh_upper_leg_link</x:v>
       </x:c>
-      <x:c r="B19" s="214" t="str">
+      <x:c r="B19" s="334" t="str">
         <x:v>LH</x:v>
       </x:c>
-      <x:c r="C19" s="214" t="str">
+      <x:c r="C19" s="334" t="str">
         <x:v>meshes/lh_upper_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D19" s="215" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="E19" s="216" t="n">
-        <x:v>0.098</x:v>
-      </x:c>
-      <x:c r="F19" s="214" t="str">
-        <x:v>Upper-leg assembly</x:v>
-      </x:c>
-      <x:c r="G19" s="214" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (32 g); ABS ESD cover (5 g)</x:v>
-      </x:c>
-      <x:c r="H19" s="214" t="str">
-        <x:v>ACT_RL_UpperLeg + Upper_Leg + Upper_Leg_Cover</x:v>
-      </x:c>
-      <x:c r="I19" s="214" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="J19" s="214" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K19" s="217" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D19" s="335" t="n">
+        <x:v>172.5</x:v>
+      </x:c>
+      <x:c r="E19" s="335" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="F19" s="334" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G19" s="334" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H19" s="334" t="str">
+        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I19" s="334" t="str">
+        <x:v>LF symmetry-derived</x:v>
+      </x:c>
+      <x:c r="J19" s="334" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K19" s="334" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="218" t="str">
+      <x:c r="A20" s="337" t="str">
         <x:v>lh_lower_leg_link</x:v>
       </x:c>
-      <x:c r="B20" s="219" t="str">
+      <x:c r="B20" s="337" t="str">
         <x:v>LH</x:v>
       </x:c>
-      <x:c r="C20" s="219" t="str">
+      <x:c r="C20" s="337" t="str">
         <x:v>meshes/lh_lower_leg_link.stl</x:v>
       </x:c>
-      <x:c r="D20" s="220" t="n">
-        <x:v>114.5</x:v>
-      </x:c>
-      <x:c r="E20" s="221" t="n">
-        <x:v>0.1145</x:v>
-      </x:c>
-      <x:c r="F20" s="219" t="str">
-        <x:v>Lower-leg assembly</x:v>
-      </x:c>
-      <x:c r="G20" s="219" t="str">
-        <x:v>Feetech ST3215 actuator assembly (61 g; internal material not specified); PPA+CF (53.5 g)</x:v>
-      </x:c>
-      <x:c r="H20" s="219" t="str">
-        <x:v>ACT_RL_LowerLeg + Lower_Leg_L</x:v>
-      </x:c>
-      <x:c r="I20" s="219" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="J20" s="219" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K20" s="222" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D20" s="338" t="n">
+        <x:v>59.5</x:v>
+      </x:c>
+      <x:c r="E20" s="338" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="F20" s="337" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G20" s="337" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H20" s="337" t="str">
+        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I20" s="337" t="str">
+        <x:v>LF symmetry-derived</x:v>
+      </x:c>
+      <x:c r="J20" s="337" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K20" s="337" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="228" t="str">
+      <x:c r="A21" s="340" t="str">
         <x:v>lh_foot_link</x:v>
       </x:c>
-      <x:c r="B21" s="229" t="str">
+      <x:c r="B21" s="340" t="str">
         <x:v>LH</x:v>
       </x:c>
-      <x:c r="C21" s="229" t="str">
+      <x:c r="C21" s="340" t="str">
         <x:v>meshes/lh_foot_link.stl</x:v>
       </x:c>
-      <x:c r="D21" s="230" t="n">
-        <x:v>6.5</x:v>
-      </x:c>
-      <x:c r="E21" s="231" t="n">
-        <x:v>0.0065</x:v>
-      </x:c>
-      <x:c r="F21" s="229" t="str">
-        <x:v>Rubber foot</x:v>
-      </x:c>
-      <x:c r="G21" s="229" t="str">
-        <x:v>TPU 95A (6.5 g)</x:v>
-      </x:c>
-      <x:c r="H21" s="229" t="str">
-        <x:v>Rubber_Foot RL</x:v>
-      </x:c>
-      <x:c r="I21" s="229" t="str">
-        <x:v>No separately measured fasteners allocated</x:v>
-      </x:c>
-      <x:c r="J21" s="229" t="str">
-        <x:v>Mass verified; CAD CoM and inertia tensor pending</x:v>
-      </x:c>
-      <x:c r="K21" s="232" t="str">
-        <x:v>Engineering metadata comment inserted</x:v>
+      <x:c r="D21" s="341" t="n">
+        <x:v>17.5</x:v>
+      </x:c>
+      <x:c r="E21" s="341" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="F21" s="340" t="str">
+        <x:v>CAD physical-property subassembly</x:v>
+      </x:c>
+      <x:c r="G21" s="340" t="str">
+        <x:v>Mass reconciliation + Solid Edge report</x:v>
+      </x:c>
+      <x:c r="H21" s="340" t="str">
+        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="I21" s="340" t="str">
+        <x:v>LF symmetry-derived</x:v>
+      </x:c>
+      <x:c r="J21" s="340" t="str">
+        <x:v>CoM + inertia tensor reconstructed at CoM</x:v>
+      </x:c>
+      <x:c r="K21" s="340" t="str">
+        <x:v>Standard URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5067,7 +5923,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74504bc9cdf148d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R019e2d942cee4562"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5076,8 +5932,8 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="52" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="44" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="44" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
@@ -5085,107 +5941,116 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="139" t="str">
+      <x:c r="A1" s="289" t="str">
         <x:v>MATDOG — Riepilogo masse REV00</x:v>
       </x:c>
-      <x:c r="B1" s="139"/>
+      <x:c r="B1" s="289"/>
       <x:c r="C1" s="139"/>
       <x:c r="D1" s="139"/>
       <x:c r="E1" s="139"/>
       <x:c r="F1" s="139"/>
     </x:row>
-    <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="144" t="str">
-        <x:v>Il totale del modello URDF corrente include body + quattro zampe. Il motore yaw testa da 61 g è presente nell’Engineering Data ma non è ancora modellato come link URDF.</x:v>
-      </x:c>
-      <x:c r="B2" s="144"/>
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="294" t="str">
+        <x:v>Baseline dinamica CAD: 17 link, 2.480 kg. Il dettaglio della riconciliazione tra CAD, calcolo pesi e misura fisica è nel foglio Mass_Reconciliation.</x:v>
+      </x:c>
+      <x:c r="B2" s="294"/>
       <x:c r="C2" s="144"/>
       <x:c r="D2" s="144"/>
       <x:c r="E2" s="144"/>
       <x:c r="F2" s="144"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="157" t="str">
+      <x:c r="A4" s="345" t="str">
         <x:v>Metric</x:v>
       </x:c>
-      <x:c r="B4" s="159" t="str">
+      <x:c r="B4" s="345" t="str">
         <x:v>Value</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="236" t="str">
+      <x:c r="A5" s="372" t="str">
         <x:v>URDF modeled links mass [g]</x:v>
       </x:c>
-      <x:c r="B5" s="233" t="n">
-        <x:f>SUM(Link_Engineering!D5:D21)</x:f>
-        <x:v>1549</x:v>
+      <x:c r="B5" s="306" t="n">
+        <x:v>2480</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="236" t="str">
+      <x:c r="A6" s="372" t="str">
         <x:v>URDF modeled links mass [kg]</x:v>
       </x:c>
-      <x:c r="B6" s="234" t="n">
-        <x:f>B5/1000</x:f>
-        <x:v>1.549</x:v>
+      <x:c r="B6" s="306" t="n">
+        <x:v>2.48</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="236" t="str">
+      <x:c r="A7" s="372" t="str">
         <x:v>Four legs mass [g]</x:v>
       </x:c>
-      <x:c r="B7" s="233" t="n">
-        <x:f>SUMIF(Link_Engineering!B5:B21,"&lt;&gt;Body",Link_Engineering!D5:D21)</x:f>
-        <x:v>1264</x:v>
+      <x:c r="B7" s="306" t="n">
+        <x:v>1198</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="236" t="str">
+      <x:c r="A8" s="372" t="str">
         <x:v>Base link mass [g]</x:v>
       </x:c>
-      <x:c r="B8" s="233" t="n">
-        <x:f>SUMIF(Link_Engineering!B5:B21,"Body",Link_Engineering!D5:D21)</x:f>
-        <x:v>285</x:v>
+      <x:c r="B8" s="306" t="n">
+        <x:v>1282</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="236" t="str">
-        <x:v>Engineering_Data total [g]</x:v>
-      </x:c>
-      <x:c r="B9" s="233" t="n">
-        <x:v>1610</x:v>
+      <x:c r="A9" s="372" t="str">
+        <x:v>CAD full assembly [g]</x:v>
+      </x:c>
+      <x:c r="B9" s="306" t="n">
+        <x:v>2480</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="236" t="str">
-        <x:v>Excluded from REV00 URDF: head yaw actuator [g]</x:v>
-      </x:c>
-      <x:c r="B10" s="233" t="n">
+      <x:c r="A10" s="372" t="str">
+        <x:v>Weight-breakdown calculated [g]</x:v>
+      </x:c>
+      <x:c r="B10" s="306" t="n">
+        <x:v>2389.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="340" t="str">
+        <x:v>Physical robot measured [g]</x:v>
+      </x:c>
+      <x:c r="B11" s="341" t="n">
+        <x:v>2297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="301" t="str">
+        <x:v>Neck yaw actuator [g]</x:v>
+      </x:c>
+      <x:c r="B12" s="306" t="n">
         <x:v>61</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="238" t="str">
-        <x:v>Mass reconciliation delta [g]</x:v>
-      </x:c>
-      <x:c r="B11" s="239" t="n">
-        <x:f>B9-B5-B10</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
     <x:row r="13">
-      <x:c r="A13" s="179" t="str">
-        <x:v>Stato simulazione: masse reali definite; baricentri e tensori d’inerzia ancora PENDING_CAD. Non sono stati inseriti blocchi &lt;inertial&gt; nel URDF per evitare parametri dinamici fittizi.</x:v>
-      </x:c>
-      <x:c r="B13" s="180"/>
+      <x:c r="A13" s="375" t="str">
+        <x:v>Standalone neck yaw link in REV00</x:v>
+      </x:c>
+      <x:c r="B13" s="375" t="str">
+        <x:v>No</x:v>
+      </x:c>
       <x:c r="C13" s="180"/>
       <x:c r="D13" s="180"/>
       <x:c r="E13" s="180"/>
       <x:c r="F13" s="181"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="182"/>
-      <x:c r="B14" s="183"/>
+      <x:c r="A14" s="375" t="str">
+        <x:v>Dynamic property status</x:v>
+      </x:c>
+      <x:c r="B14" s="375" t="str">
+        <x:v>CAD CoM + inertia tensor inserted</x:v>
+      </x:c>
       <x:c r="C14" s="183"/>
       <x:c r="D14" s="183"/>
       <x:c r="E14" s="183"/>
@@ -5197,6 +6062,8 @@
     <x:mergeCell ref="A2:F2"/>
     <x:mergeCell ref="A13:F13"/>
     <x:mergeCell ref="A13:F14"/>
+    <x:mergeCell ref="A1:B1"/>
+    <x:mergeCell ref="A2:B2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5219,32 +6086,32 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="139" t="str">
-        <x:v>Engineering_Data.xlsx — Weight source imported into MATDOG canonical workbook</x:v>
-      </x:c>
-      <x:c r="B1" s="139"/>
-      <x:c r="C1" s="139"/>
-      <x:c r="D1" s="139"/>
-      <x:c r="E1" s="139"/>
-      <x:c r="F1" s="139"/>
-      <x:c r="G1" s="139"/>
-      <x:c r="H1" s="139"/>
-      <x:c r="I1" s="139"/>
-      <x:c r="J1" s="139"/>
-    </x:row>
-    <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="144" t="str">
-        <x:v>Fonte: Engineering_Data.xlsx / Weight. La colonna finale mostra l’assegnazione al link URDF; il motore yaw testa non è ancora presente nel modello REV00.</x:v>
-      </x:c>
-      <x:c r="B2" s="144"/>
-      <x:c r="C2" s="144"/>
-      <x:c r="D2" s="144"/>
-      <x:c r="E2" s="144"/>
-      <x:c r="F2" s="144"/>
-      <x:c r="G2" s="144"/>
-      <x:c r="H2" s="144"/>
-      <x:c r="I2" s="144"/>
-      <x:c r="J2" s="144"/>
+      <x:c r="A1" s="289" t="str">
+        <x:v>Engineering_Data.xlsx — Historical weight source / reconciliation input</x:v>
+      </x:c>
+      <x:c r="B1" s="289"/>
+      <x:c r="C1" s="289"/>
+      <x:c r="D1" s="289"/>
+      <x:c r="E1" s="289"/>
+      <x:c r="F1" s="289"/>
+      <x:c r="G1" s="289"/>
+      <x:c r="H1" s="289"/>
+      <x:c r="I1" s="289"/>
+      <x:c r="J1" s="289"/>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="294" t="str">
+        <x:v>Historical component allocation retained for traceability. It is not the dynamic source of truth: masses and inertias now come from Solid Edge physical-property exports plus the CAD mass reconciliation in Inertial_Properties and Mass_Reconciliation.</x:v>
+      </x:c>
+      <x:c r="B2" s="294"/>
+      <x:c r="C2" s="294"/>
+      <x:c r="D2" s="294"/>
+      <x:c r="E2" s="294"/>
+      <x:c r="F2" s="294"/>
+      <x:c r="G2" s="294"/>
+      <x:c r="H2" s="294"/>
+      <x:c r="I2" s="294"/>
+      <x:c r="J2" s="294"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="157" t="str">
@@ -6528,233 +7395,233 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="55" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="50" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="68" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="54" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="23" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="275" t="str">
-        <x:v>MATDOG — Audit pulizia URDF / revisione lower limit -92°</x:v>
-      </x:c>
-      <x:c r="B1" s="275"/>
-      <x:c r="C1" s="275"/>
-      <x:c r="D1" s="275"/>
-      <x:c r="E1" s="275"/>
+      <x:c r="A1" s="289" t="str">
+        <x:v>MATDOG — Audit URDF REV00 con proprietà dinamiche</x:v>
+      </x:c>
+      <x:c r="B1" s="289"/>
+      <x:c r="C1" s="289"/>
+      <x:c r="D1" s="289"/>
+      <x:c r="E1" s="289"/>
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="279" t="str">
-        <x:v>Audit effettuato sul file URDF consolidato: struttura, riferimenti mesh, trasformazioni, limiti e coerenza parent/child.</x:v>
-      </x:c>
-      <x:c r="B2" s="279"/>
-      <x:c r="C2" s="279"/>
-      <x:c r="D2" s="279"/>
-      <x:c r="E2" s="279"/>
+      <x:c r="A2" s="294" t="str">
+        <x:v>Audit aggiornato: struttura, riferimenti mesh, origini visual/collision, limiti, masse CAD, CoM per-link e tensori d’inerzia.</x:v>
+      </x:c>
+      <x:c r="B2" s="294"/>
+      <x:c r="C2" s="294"/>
+      <x:c r="D2" s="294"/>
+      <x:c r="E2" s="294"/>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
-      <x:c r="A4" s="284" t="str">
+      <x:c r="A4" s="390" t="str">
         <x:v>Area</x:v>
       </x:c>
-      <x:c r="B4" s="284" t="str">
+      <x:c r="B4" s="390" t="str">
         <x:v>Esito</x:v>
       </x:c>
-      <x:c r="C4" s="284" t="str">
+      <x:c r="C4" s="390" t="str">
         <x:v>Dettaglio</x:v>
       </x:c>
-      <x:c r="D4" s="284" t="str">
+      <x:c r="D4" s="390" t="str">
         <x:v>Azione</x:v>
       </x:c>
-      <x:c r="E4" s="284" t="str">
+      <x:c r="E4" s="390" t="str">
         <x:v>Stato</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="38" customHeight="1">
-      <x:c r="A5" s="285" t="str">
+      <x:c r="A5" s="301" t="str">
         <x:v>Struttura</x:v>
       </x:c>
-      <x:c r="B5" s="285" t="str">
+      <x:c r="B5" s="301" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="C5" s="285" t="str">
+      <x:c r="C5" s="301" t="str">
         <x:v>17 link · 16 joint · singola root: base_link.</x:v>
       </x:c>
-      <x:c r="D5" s="285" t="str">
+      <x:c r="D5" s="301" t="str">
         <x:v>Nessuna.</x:v>
       </x:c>
-      <x:c r="E5" s="285" t="str">
+      <x:c r="E5" s="301" t="str">
         <x:v>Pulito</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
-      <x:c r="A6" s="285" t="str">
+      <x:c r="A6" s="301" t="str">
         <x:v>Catene cinematiche</x:v>
       </x:c>
-      <x:c r="B6" s="285" t="str">
+      <x:c r="B6" s="301" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="C6" s="285" t="str">
+      <x:c r="C6" s="301" t="str">
         <x:v>4 catene complete: hip → upper → lower → foot.</x:v>
       </x:c>
-      <x:c r="D6" s="285" t="str">
+      <x:c r="D6" s="301" t="str">
         <x:v>Nessuna.</x:v>
       </x:c>
-      <x:c r="E6" s="285" t="str">
+      <x:c r="E6" s="301" t="str">
         <x:v>Pulito</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="38" customHeight="1">
-      <x:c r="A7" s="285" t="str">
+      <x:c r="A7" s="301" t="str">
         <x:v>Coordinate joint</x:v>
       </x:c>
-      <x:c r="B7" s="285" t="str">
+      <x:c r="B7" s="301" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="C7" s="285" t="str">
+      <x:c r="C7" s="301" t="str">
         <x:v>Tutti gli origin joint sono nel parent-link frame; rpy joint = 0.</x:v>
       </x:c>
-      <x:c r="D7" s="285" t="str">
+      <x:c r="D7" s="301" t="str">
         <x:v>Nessuna.</x:v>
       </x:c>
-      <x:c r="E7" s="285" t="str">
+      <x:c r="E7" s="301" t="str">
         <x:v>Pulito</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="38" customHeight="1">
-      <x:c r="A8" s="285" t="str">
+      <x:c r="A8" s="301" t="str">
         <x:v>Lower leg limits</x:v>
       </x:c>
-      <x:c r="B8" s="285" t="str">
+      <x:c r="B8" s="301" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="C8" s="285" t="str">
+      <x:c r="C8" s="301" t="str">
         <x:v>4 joint: θmin = -92° (-1.605702911835 rad) · θmax = +37.5°.</x:v>
       </x:c>
-      <x:c r="D8" s="285" t="str">
+      <x:c r="D8" s="301" t="str">
         <x:v>Aggiornati nella presente revisione.</x:v>
       </x:c>
-      <x:c r="E8" s="285" t="str">
+      <x:c r="E8" s="301" t="str">
         <x:v>Canonico</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="38" customHeight="1">
-      <x:c r="A9" s="285" t="str">
+      <x:c r="A9" s="301" t="str">
         <x:v>Upper leg limits</x:v>
       </x:c>
-      <x:c r="B9" s="285" t="str">
+      <x:c r="B9" s="301" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="C9" s="285" t="str">
+      <x:c r="C9" s="301" t="str">
         <x:v>4 joint: θmin = -52.5° · θmax = +122.5°.</x:v>
       </x:c>
-      <x:c r="D9" s="285" t="str">
+      <x:c r="D9" s="301" t="str">
         <x:v>Nessuna.</x:v>
       </x:c>
-      <x:c r="E9" s="285" t="str">
+      <x:c r="E9" s="301" t="str">
         <x:v>Canonico</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="38" customHeight="1">
-      <x:c r="A10" s="285" t="str">
+      <x:c r="A10" s="301" t="str">
         <x:v>Mesh references</x:v>
       </x:c>
-      <x:c r="B10" s="285" t="str">
+      <x:c r="B10" s="301" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="C10" s="285" t="str">
+      <x:c r="C10" s="301" t="str">
         <x:v>34 riferimenti mesh (visual + collision), tutti relativi a meshes/*.stl; 17 asset unici.</x:v>
       </x:c>
-      <x:c r="D10" s="285" t="str">
+      <x:c r="D10" s="301" t="str">
         <x:v>Nessuna.</x:v>
       </x:c>
-      <x:c r="E10" s="285" t="str">
+      <x:c r="E10" s="301" t="str">
         <x:v>Pulito</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="38" customHeight="1">
-      <x:c r="A11" s="285" t="str">
-        <x:v>Mesh transforms</x:v>
-      </x:c>
-      <x:c r="B11" s="285" t="str">
+      <x:c r="A11" s="301" t="str">
+        <x:v>Mesh origins</x:v>
+      </x:c>
+      <x:c r="B11" s="301" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="C11" s="285" t="str">
-        <x:v>13 link: xyz 0,0,0 · rpy 0,0,0. 4 upper link: xyz 0,0,-0.090 · rpy 0,180°,0.</x:v>
-      </x:c>
-      <x:c r="D11" s="285" t="str">
-        <x:v>Il solo offset non nullo è necessario al pivot/verso delle mesh upper asimmetriche.</x:v>
-      </x:c>
-      <x:c r="E11" s="285" t="str">
+      <x:c r="C11" s="301" t="str">
+        <x:v>17 link: visual e collision usano xyz 0,0,0 · rpy 0,0,0.</x:v>
+      </x:c>
+      <x:c r="D11" s="301" t="str">
+        <x:v>Nessuna.</x:v>
+      </x:c>
+      <x:c r="E11" s="301" t="str">
         <x:v>Pulito</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="38" customHeight="1">
-      <x:c r="A12" s="285" t="str">
+      <x:c r="A12" s="301" t="str">
         <x:v>Visual / Collision</x:v>
       </x:c>
-      <x:c r="B12" s="285" t="str">
+      <x:c r="B12" s="301" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="C12" s="285" t="str">
+      <x:c r="C12" s="301" t="str">
         <x:v>Per ciascun link visual e collision usano stessa mesh e stessa origin.</x:v>
       </x:c>
-      <x:c r="D12" s="285" t="str">
+      <x:c r="D12" s="301" t="str">
         <x:v>Scelta attuale conservata.</x:v>
       </x:c>
-      <x:c r="E12" s="285" t="str">
+      <x:c r="E12" s="301" t="str">
         <x:v>Coerente</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="38" customHeight="1">
-      <x:c r="A13" s="285" t="str">
-        <x:v>Materiali e masse</x:v>
-      </x:c>
-      <x:c r="B13" s="285" t="str">
+      <x:c r="A13" s="391" t="str">
+        <x:v>Masses + CoM</x:v>
+      </x:c>
+      <x:c r="B13" s="391" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C13" s="391" t="str">
+        <x:v>2.480 kg from CAD reconciliation; every modeled link has a CAD CoM in its local URDF frame.</x:v>
+      </x:c>
+      <x:c r="D13" s="391" t="str">
+        <x:v>Inserted in standard &lt;inertial&gt; blocks.</x:v>
+      </x:c>
+      <x:c r="E13" s="391" t="str">
+        <x:v>Simulation-ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="38" customHeight="1">
+      <x:c r="A14" s="391" t="str">
+        <x:v>Inertia tensors</x:v>
+      </x:c>
+      <x:c r="B14" s="391" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C14" s="391" t="str">
+        <x:v>Tensors reconstructed at CoM from principal axes + radii of gyration; symmetry-derived legs aggregate-check against full CAD assembly.</x:v>
+      </x:c>
+      <x:c r="D14" s="391" t="str">
+        <x:v>Inserted in standard &lt;inertial&gt; blocks.</x:v>
+      </x:c>
+      <x:c r="E14" s="391" t="str">
+        <x:v>Simulation-ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="38" customHeight="1">
+      <x:c r="A15" s="392" t="str">
+        <x:v>Neck yaw scope</x:v>
+      </x:c>
+      <x:c r="B15" s="392" t="str">
         <x:v>INFO</x:v>
       </x:c>
-      <x:c r="C13" s="285" t="str">
-        <x:v>Masse/materiali documentati come metadata. Non ci sono blocchi &lt;inertial&gt; standard.</x:v>
-      </x:c>
-      <x:c r="D13" s="285" t="str">
-        <x:v>Estrarre CoM + tensore d’inerzia dal CAD prima della dinamica.</x:v>
-      </x:c>
-      <x:c r="E13" s="285" t="str">
-        <x:v>Da completare</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="38" customHeight="1">
-      <x:c r="A14" s="285" t="str">
-        <x:v>Collisioni fisiche</x:v>
-      </x:c>
-      <x:c r="B14" s="285" t="str">
-        <x:v>INFO</x:v>
-      </x:c>
-      <x:c r="C14" s="285" t="str">
-        <x:v>Mesh collision reali corrette per controlli geometrici.</x:v>
-      </x:c>
-      <x:c r="D14" s="285" t="str">
-        <x:v>Prima di simulazione dinamica sostituire con primitive/mesh semplificate.</x:v>
-      </x:c>
-      <x:c r="E14" s="285" t="str">
-        <x:v>Futuro</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="38" customHeight="1">
-      <x:c r="A15" s="285" t="str">
-        <x:v>Semplificazione possibile</x:v>
-      </x:c>
-      <x:c r="B15" s="285" t="str">
-        <x:v>INFO</x:v>
-      </x:c>
-      <x:c r="C15" s="285" t="str">
-        <x:v>Il transform upper può sparire solo riesportando gli STL upper già allineati al frame URDF.</x:v>
-      </x:c>
-      <x:c r="D15" s="285" t="str">
-        <x:v>Non consigliato ora: il file attuale è pulito e verificato.</x:v>
-      </x:c>
-      <x:c r="E15" s="285" t="str">
-        <x:v>Opzionale</x:v>
+      <x:c r="C15" s="392" t="str">
+        <x:v>No standalone neck yaw link or mounted-frame inertial report is included in REV00.</x:v>
+      </x:c>
+      <x:c r="D15" s="392" t="str">
+        <x:v>Keep excluded until dedicated CAD export is available.</x:v>
+      </x:c>
+      <x:c r="E15" s="392" t="str">
+        <x:v>Controlled scope</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6774,4 +7641,1519 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="8" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="21" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="19" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="40" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="48" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="289" t="str">
+        <x:v>MATDOG — Proprietà inerziali REV00</x:v>
+      </x:c>
+      <x:c r="B1" s="289"/>
+      <x:c r="C1" s="289"/>
+      <x:c r="D1" s="289"/>
+      <x:c r="E1" s="289"/>
+      <x:c r="F1" s="289"/>
+      <x:c r="G1" s="289"/>
+      <x:c r="H1" s="289"/>
+      <x:c r="I1" s="289"/>
+      <x:c r="J1" s="289"/>
+      <x:c r="K1" s="289"/>
+      <x:c r="L1" s="289"/>
+      <x:c r="M1" s="289"/>
+      <x:c r="N1" s="289"/>
+      <x:c r="O1" s="289"/>
+      <x:c r="P1" s="289"/>
+      <x:c r="Q1" s="289"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="294" t="str">
+        <x:v>Fonte canonica per il modello dinamico: masse CAD riconciliate, baricentri per-link e tensori d’inerzia al centro di massa, espressi nei frame URDF dei link.</x:v>
+      </x:c>
+      <x:c r="B2" s="294"/>
+      <x:c r="C2" s="294"/>
+      <x:c r="D2" s="294"/>
+      <x:c r="E2" s="294"/>
+      <x:c r="F2" s="294"/>
+      <x:c r="G2" s="294"/>
+      <x:c r="H2" s="294"/>
+      <x:c r="I2" s="294"/>
+      <x:c r="J2" s="294"/>
+      <x:c r="K2" s="294"/>
+      <x:c r="L2" s="294"/>
+      <x:c r="M2" s="294"/>
+      <x:c r="N2" s="294"/>
+      <x:c r="O2" s="294"/>
+      <x:c r="P2" s="294"/>
+      <x:c r="Q2" s="294"/>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="300" t="str">
+        <x:v>Link</x:v>
+      </x:c>
+      <x:c r="B4" s="300" t="str">
+        <x:v>Leg</x:v>
+      </x:c>
+      <x:c r="C4" s="300" t="str">
+        <x:v>CAD subassembly</x:v>
+      </x:c>
+      <x:c r="D4" s="300" t="str">
+        <x:v>Mass
+[kg]</x:v>
+      </x:c>
+      <x:c r="E4" s="300" t="str">
+        <x:v>CoM X
+[m]</x:v>
+      </x:c>
+      <x:c r="F4" s="300" t="str">
+        <x:v>CoM Y
+[m]</x:v>
+      </x:c>
+      <x:c r="G4" s="300" t="str">
+        <x:v>CoM Z
+[m]</x:v>
+      </x:c>
+      <x:c r="H4" s="300" t="str">
+        <x:v>Ixx
+[kg·m²]</x:v>
+      </x:c>
+      <x:c r="I4" s="300" t="str">
+        <x:v>Ixy
+[kg·m²]</x:v>
+      </x:c>
+      <x:c r="J4" s="300" t="str">
+        <x:v>Ixz
+[kg·m²]</x:v>
+      </x:c>
+      <x:c r="K4" s="300" t="str">
+        <x:v>Iyy
+[kg·m²]</x:v>
+      </x:c>
+      <x:c r="L4" s="300" t="str">
+        <x:v>Iyz
+[kg·m²]</x:v>
+      </x:c>
+      <x:c r="M4" s="300" t="str">
+        <x:v>Izz
+[kg·m²]</x:v>
+      </x:c>
+      <x:c r="N4" s="300" t="str">
+        <x:v>Evidence</x:v>
+      </x:c>
+      <x:c r="O4" s="300" t="str">
+        <x:v>Derivation / symmetry rule</x:v>
+      </x:c>
+      <x:c r="P4" s="300" t="str">
+        <x:v>Source files</x:v>
+      </x:c>
+      <x:c r="Q4" s="300" t="str">
+        <x:v>URDF state</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="301" t="str">
+        <x:v>base_link</x:v>
+      </x:c>
+      <x:c r="B5" s="301" t="str">
+        <x:v>Body</x:v>
+      </x:c>
+      <x:c r="C5" s="301" t="str">
+        <x:v>Base assembly</x:v>
+      </x:c>
+      <x:c r="D5" s="303" t="n">
+        <x:v>1.282</x:v>
+      </x:c>
+      <x:c r="E5" s="303" t="n">
+        <x:v>0.00584</x:v>
+      </x:c>
+      <x:c r="F5" s="303" t="n">
+        <x:v>-0.00065</x:v>
+      </x:c>
+      <x:c r="G5" s="303" t="n">
+        <x:v>0.02773</x:v>
+      </x:c>
+      <x:c r="H5" s="302" t="n">
+        <x:v>0.00147265728657</x:v>
+      </x:c>
+      <x:c r="I5" s="302" t="n">
+        <x:v>0.0000142294028465</x:v>
+      </x:c>
+      <x:c r="J5" s="302" t="n">
+        <x:v>-0.000443609672652</x:v>
+      </x:c>
+      <x:c r="K5" s="302" t="n">
+        <x:v>0.00887012995059</x:v>
+      </x:c>
+      <x:c r="L5" s="302" t="n">
+        <x:v>-0.00000770141299896</x:v>
+      </x:c>
+      <x:c r="M5" s="302" t="n">
+        <x:v>0.00949906085204</x:v>
+      </x:c>
+      <x:c r="N5" s="301" t="str">
+        <x:v>DIRECT CAD</x:v>
+      </x:c>
+      <x:c r="O5" s="301" t="str">
+        <x:v>CAD direct: principal axes + radii of gyration</x:v>
+      </x:c>
+      <x:c r="P5" s="301" t="str">
+        <x:v>physprop__base_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q5" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="301" t="str">
+        <x:v>lf_hip_link</x:v>
+      </x:c>
+      <x:c r="B6" s="301" t="str">
+        <x:v>LF</x:v>
+      </x:c>
+      <x:c r="C6" s="301" t="str">
+        <x:v>Hip subassembly</x:v>
+      </x:c>
+      <x:c r="D6" s="303" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="E6" s="303" t="n">
+        <x:v>0.00366</x:v>
+      </x:c>
+      <x:c r="F6" s="303" t="n">
+        <x:v>0.02982</x:v>
+      </x:c>
+      <x:c r="G6" s="303" t="n">
+        <x:v>0.00694</x:v>
+      </x:c>
+      <x:c r="H6" s="302" t="n">
+        <x:v>0.0000402252347591</x:v>
+      </x:c>
+      <x:c r="I6" s="302" t="n">
+        <x:v>-0.00000131462768927</x:v>
+      </x:c>
+      <x:c r="J6" s="302" t="n">
+        <x:v>-0.00000113953716339</x:v>
+      </x:c>
+      <x:c r="K6" s="302" t="n">
+        <x:v>0.000018958128496</x:v>
+      </x:c>
+      <x:c r="L6" s="302" t="n">
+        <x:v>-0.00000446400670021</x:v>
+      </x:c>
+      <x:c r="M6" s="302" t="n">
+        <x:v>0.0000454280867449</x:v>
+      </x:c>
+      <x:c r="N6" s="301" t="str">
+        <x:v>DIRECT CAD</x:v>
+      </x:c>
+      <x:c r="O6" s="301" t="str">
+        <x:v>CAD direct: principal axes + radii of gyration</x:v>
+      </x:c>
+      <x:c r="P6" s="301" t="str">
+        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q6" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="301" t="str">
+        <x:v>lf_upper_leg_link</x:v>
+      </x:c>
+      <x:c r="B7" s="301" t="str">
+        <x:v>LF</x:v>
+      </x:c>
+      <x:c r="C7" s="301" t="str">
+        <x:v>Upper-leg subassembly</x:v>
+      </x:c>
+      <x:c r="D7" s="303" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="E7" s="303" t="n">
+        <x:v>0.00108</x:v>
+      </x:c>
+      <x:c r="F7" s="303" t="n">
+        <x:v>0.00015</x:v>
+      </x:c>
+      <x:c r="G7" s="303" t="n">
+        <x:v>-0.04503</x:v>
+      </x:c>
+      <x:c r="H7" s="302" t="n">
+        <x:v>0.000205436660094</x:v>
+      </x:c>
+      <x:c r="I7" s="302" t="n">
+        <x:v>-5.63507198417e-8</x:v>
+      </x:c>
+      <x:c r="J7" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="302" t="n">
+        <x:v>0.000199175976156</x:v>
+      </x:c>
+      <x:c r="L7" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="302" t="n">
+        <x:v>0.00003111294525</x:v>
+      </x:c>
+      <x:c r="N7" s="301" t="str">
+        <x:v>DIRECT CAD</x:v>
+      </x:c>
+      <x:c r="O7" s="301" t="str">
+        <x:v>CAD direct: principal axes + radii of gyration</x:v>
+      </x:c>
+      <x:c r="P7" s="301" t="str">
+        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q7" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="301" t="str">
+        <x:v>lf_lower_leg_link</x:v>
+      </x:c>
+      <x:c r="B8" s="301" t="str">
+        <x:v>LF</x:v>
+      </x:c>
+      <x:c r="C8" s="301" t="str">
+        <x:v>Lower-leg subassembly</x:v>
+      </x:c>
+      <x:c r="D8" s="303" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="E8" s="303" t="n">
+        <x:v>0.03075</x:v>
+      </x:c>
+      <x:c r="F8" s="303" t="n">
+        <x:v>-0.00118</x:v>
+      </x:c>
+      <x:c r="G8" s="303" t="n">
+        <x:v>-0.01958</x:v>
+      </x:c>
+      <x:c r="H8" s="302" t="n">
+        <x:v>0.0000215172642767</x:v>
+      </x:c>
+      <x:c r="I8" s="302" t="n">
+        <x:v>6.0930015348e-7</x:v>
+      </x:c>
+      <x:c r="J8" s="302" t="n">
+        <x:v>0.0000168302311374</x:v>
+      </x:c>
+      <x:c r="K8" s="302" t="n">
+        <x:v>0.000102530052784</x:v>
+      </x:c>
+      <x:c r="L8" s="302" t="n">
+        <x:v>-3.71953235117e-7</x:v>
+      </x:c>
+      <x:c r="M8" s="302" t="n">
+        <x:v>0.000104321477439</x:v>
+      </x:c>
+      <x:c r="N8" s="301" t="str">
+        <x:v>DIRECT CAD</x:v>
+      </x:c>
+      <x:c r="O8" s="301" t="str">
+        <x:v>CAD direct: principal axes + radii of gyration</x:v>
+      </x:c>
+      <x:c r="P8" s="301" t="str">
+        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q8" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="301" t="str">
+        <x:v>lf_foot_link</x:v>
+      </x:c>
+      <x:c r="B9" s="301" t="str">
+        <x:v>LF</x:v>
+      </x:c>
+      <x:c r="C9" s="301" t="str">
+        <x:v>Foot subassembly</x:v>
+      </x:c>
+      <x:c r="D9" s="303" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="E9" s="303" t="n">
+        <x:v>-0.00052</x:v>
+      </x:c>
+      <x:c r="F9" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="303" t="n">
+        <x:v>0.01548</x:v>
+      </x:c>
+      <x:c r="H9" s="302" t="n">
+        <x:v>0.00000114526961866</x:v>
+      </x:c>
+      <x:c r="I9" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="302" t="n">
+        <x:v>-1.55064671079e-8</x:v>
+      </x:c>
+      <x:c r="K9" s="302" t="n">
+        <x:v>0.00000120267175</x:v>
+      </x:c>
+      <x:c r="L9" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="302" t="n">
+        <x:v>0.00000114835213134</x:v>
+      </x:c>
+      <x:c r="N9" s="301" t="str">
+        <x:v>DIRECT CAD</x:v>
+      </x:c>
+      <x:c r="O9" s="301" t="str">
+        <x:v>CAD direct: principal axes + radii of gyration</x:v>
+      </x:c>
+      <x:c r="P9" s="301" t="str">
+        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q9" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="301" t="str">
+        <x:v>rf_hip_link</x:v>
+      </x:c>
+      <x:c r="B10" s="301" t="str">
+        <x:v>RF</x:v>
+      </x:c>
+      <x:c r="C10" s="301" t="str">
+        <x:v>Hip subassembly</x:v>
+      </x:c>
+      <x:c r="D10" s="303" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="E10" s="303" t="n">
+        <x:v>0.00366</x:v>
+      </x:c>
+      <x:c r="F10" s="303" t="n">
+        <x:v>-0.02982</x:v>
+      </x:c>
+      <x:c r="G10" s="303" t="n">
+        <x:v>0.00694</x:v>
+      </x:c>
+      <x:c r="H10" s="302" t="n">
+        <x:v>0.0000402252347591</x:v>
+      </x:c>
+      <x:c r="I10" s="302" t="n">
+        <x:v>0.00000131462768927</x:v>
+      </x:c>
+      <x:c r="J10" s="302" t="n">
+        <x:v>-0.00000113953716339</x:v>
+      </x:c>
+      <x:c r="K10" s="302" t="n">
+        <x:v>0.000018958128496</x:v>
+      </x:c>
+      <x:c r="L10" s="302" t="n">
+        <x:v>0.00000446400670021</x:v>
+      </x:c>
+      <x:c r="M10" s="302" t="n">
+        <x:v>0.0000454280867449</x:v>
+      </x:c>
+      <x:c r="N10" s="301" t="str">
+        <x:v>DERIVED BY SYMMETRY</x:v>
+      </x:c>
+      <x:c r="O10" s="301" t="str">
+        <x:v>CAD symmetry-derived from LF: local Y reflection</x:v>
+      </x:c>
+      <x:c r="P10" s="301" t="str">
+        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q10" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="301" t="str">
+        <x:v>rf_upper_leg_link</x:v>
+      </x:c>
+      <x:c r="B11" s="301" t="str">
+        <x:v>RF</x:v>
+      </x:c>
+      <x:c r="C11" s="301" t="str">
+        <x:v>Upper-leg subassembly</x:v>
+      </x:c>
+      <x:c r="D11" s="303" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="E11" s="303" t="n">
+        <x:v>0.00108</x:v>
+      </x:c>
+      <x:c r="F11" s="303" t="n">
+        <x:v>-0.00015</x:v>
+      </x:c>
+      <x:c r="G11" s="303" t="n">
+        <x:v>-0.04503</x:v>
+      </x:c>
+      <x:c r="H11" s="302" t="n">
+        <x:v>0.000205436660094</x:v>
+      </x:c>
+      <x:c r="I11" s="302" t="n">
+        <x:v>5.63507198417e-8</x:v>
+      </x:c>
+      <x:c r="J11" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" s="302" t="n">
+        <x:v>0.000199175976156</x:v>
+      </x:c>
+      <x:c r="L11" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="302" t="n">
+        <x:v>0.00003111294525</x:v>
+      </x:c>
+      <x:c r="N11" s="301" t="str">
+        <x:v>DERIVED BY SYMMETRY</x:v>
+      </x:c>
+      <x:c r="O11" s="301" t="str">
+        <x:v>CAD symmetry-derived from LF: local Y reflection</x:v>
+      </x:c>
+      <x:c r="P11" s="301" t="str">
+        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q11" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="301" t="str">
+        <x:v>rf_lower_leg_link</x:v>
+      </x:c>
+      <x:c r="B12" s="301" t="str">
+        <x:v>RF</x:v>
+      </x:c>
+      <x:c r="C12" s="301" t="str">
+        <x:v>Lower-leg subassembly</x:v>
+      </x:c>
+      <x:c r="D12" s="303" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="E12" s="303" t="n">
+        <x:v>0.03075</x:v>
+      </x:c>
+      <x:c r="F12" s="303" t="n">
+        <x:v>0.00118</x:v>
+      </x:c>
+      <x:c r="G12" s="303" t="n">
+        <x:v>-0.01958</x:v>
+      </x:c>
+      <x:c r="H12" s="302" t="n">
+        <x:v>0.0000215172642767</x:v>
+      </x:c>
+      <x:c r="I12" s="302" t="n">
+        <x:v>-6.0930015348e-7</x:v>
+      </x:c>
+      <x:c r="J12" s="302" t="n">
+        <x:v>0.0000168302311374</x:v>
+      </x:c>
+      <x:c r="K12" s="302" t="n">
+        <x:v>0.000102530052784</x:v>
+      </x:c>
+      <x:c r="L12" s="302" t="n">
+        <x:v>3.71953235117e-7</x:v>
+      </x:c>
+      <x:c r="M12" s="302" t="n">
+        <x:v>0.000104321477439</x:v>
+      </x:c>
+      <x:c r="N12" s="301" t="str">
+        <x:v>DERIVED BY SYMMETRY</x:v>
+      </x:c>
+      <x:c r="O12" s="301" t="str">
+        <x:v>CAD symmetry-derived from LF: local Y reflection</x:v>
+      </x:c>
+      <x:c r="P12" s="301" t="str">
+        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q12" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="301" t="str">
+        <x:v>rf_foot_link</x:v>
+      </x:c>
+      <x:c r="B13" s="301" t="str">
+        <x:v>RF</x:v>
+      </x:c>
+      <x:c r="C13" s="301" t="str">
+        <x:v>Foot subassembly</x:v>
+      </x:c>
+      <x:c r="D13" s="303" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="E13" s="303" t="n">
+        <x:v>-0.00052</x:v>
+      </x:c>
+      <x:c r="F13" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="303" t="n">
+        <x:v>0.01548</x:v>
+      </x:c>
+      <x:c r="H13" s="302" t="n">
+        <x:v>0.00000114526961866</x:v>
+      </x:c>
+      <x:c r="I13" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="302" t="n">
+        <x:v>-1.55064671079e-8</x:v>
+      </x:c>
+      <x:c r="K13" s="302" t="n">
+        <x:v>0.00000120267175</x:v>
+      </x:c>
+      <x:c r="L13" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="302" t="n">
+        <x:v>0.00000114835213134</x:v>
+      </x:c>
+      <x:c r="N13" s="301" t="str">
+        <x:v>DERIVED BY SYMMETRY</x:v>
+      </x:c>
+      <x:c r="O13" s="301" t="str">
+        <x:v>CAD symmetry-derived from LF: identical foot geometry</x:v>
+      </x:c>
+      <x:c r="P13" s="301" t="str">
+        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q13" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="301" t="str">
+        <x:v>rh_hip_link</x:v>
+      </x:c>
+      <x:c r="B14" s="301" t="str">
+        <x:v>RH</x:v>
+      </x:c>
+      <x:c r="C14" s="301" t="str">
+        <x:v>Hip subassembly</x:v>
+      </x:c>
+      <x:c r="D14" s="303" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="E14" s="303" t="n">
+        <x:v>0.00366</x:v>
+      </x:c>
+      <x:c r="F14" s="303" t="n">
+        <x:v>-0.02982</x:v>
+      </x:c>
+      <x:c r="G14" s="303" t="n">
+        <x:v>0.00694</x:v>
+      </x:c>
+      <x:c r="H14" s="302" t="n">
+        <x:v>0.0000402252347591</x:v>
+      </x:c>
+      <x:c r="I14" s="302" t="n">
+        <x:v>0.00000131462768927</x:v>
+      </x:c>
+      <x:c r="J14" s="302" t="n">
+        <x:v>-0.00000113953716339</x:v>
+      </x:c>
+      <x:c r="K14" s="302" t="n">
+        <x:v>0.000018958128496</x:v>
+      </x:c>
+      <x:c r="L14" s="302" t="n">
+        <x:v>0.00000446400670021</x:v>
+      </x:c>
+      <x:c r="M14" s="302" t="n">
+        <x:v>0.0000454280867449</x:v>
+      </x:c>
+      <x:c r="N14" s="301" t="str">
+        <x:v>DERIVED BY SYMMETRY</x:v>
+      </x:c>
+      <x:c r="O14" s="301" t="str">
+        <x:v>CAD symmetry-derived from LF: local Y reflection</x:v>
+      </x:c>
+      <x:c r="P14" s="301" t="str">
+        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q14" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="301" t="str">
+        <x:v>rh_upper_leg_link</x:v>
+      </x:c>
+      <x:c r="B15" s="301" t="str">
+        <x:v>RH</x:v>
+      </x:c>
+      <x:c r="C15" s="301" t="str">
+        <x:v>Upper-leg subassembly</x:v>
+      </x:c>
+      <x:c r="D15" s="303" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="E15" s="303" t="n">
+        <x:v>0.00108</x:v>
+      </x:c>
+      <x:c r="F15" s="303" t="n">
+        <x:v>-0.00015</x:v>
+      </x:c>
+      <x:c r="G15" s="303" t="n">
+        <x:v>-0.04503</x:v>
+      </x:c>
+      <x:c r="H15" s="302" t="n">
+        <x:v>0.000205436660094</x:v>
+      </x:c>
+      <x:c r="I15" s="302" t="n">
+        <x:v>5.63507198417e-8</x:v>
+      </x:c>
+      <x:c r="J15" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="302" t="n">
+        <x:v>0.000199175976156</x:v>
+      </x:c>
+      <x:c r="L15" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="302" t="n">
+        <x:v>0.00003111294525</x:v>
+      </x:c>
+      <x:c r="N15" s="301" t="str">
+        <x:v>DERIVED BY SYMMETRY</x:v>
+      </x:c>
+      <x:c r="O15" s="301" t="str">
+        <x:v>CAD symmetry-derived from LF: local Y reflection</x:v>
+      </x:c>
+      <x:c r="P15" s="301" t="str">
+        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q15" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="301" t="str">
+        <x:v>rh_lower_leg_link</x:v>
+      </x:c>
+      <x:c r="B16" s="301" t="str">
+        <x:v>RH</x:v>
+      </x:c>
+      <x:c r="C16" s="301" t="str">
+        <x:v>Lower-leg subassembly</x:v>
+      </x:c>
+      <x:c r="D16" s="303" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="E16" s="303" t="n">
+        <x:v>0.03075</x:v>
+      </x:c>
+      <x:c r="F16" s="303" t="n">
+        <x:v>0.00118</x:v>
+      </x:c>
+      <x:c r="G16" s="303" t="n">
+        <x:v>-0.01958</x:v>
+      </x:c>
+      <x:c r="H16" s="302" t="n">
+        <x:v>0.0000215172642767</x:v>
+      </x:c>
+      <x:c r="I16" s="302" t="n">
+        <x:v>-6.0930015348e-7</x:v>
+      </x:c>
+      <x:c r="J16" s="302" t="n">
+        <x:v>0.0000168302311374</x:v>
+      </x:c>
+      <x:c r="K16" s="302" t="n">
+        <x:v>0.000102530052784</x:v>
+      </x:c>
+      <x:c r="L16" s="302" t="n">
+        <x:v>3.71953235117e-7</x:v>
+      </x:c>
+      <x:c r="M16" s="302" t="n">
+        <x:v>0.000104321477439</x:v>
+      </x:c>
+      <x:c r="N16" s="301" t="str">
+        <x:v>DERIVED BY SYMMETRY</x:v>
+      </x:c>
+      <x:c r="O16" s="301" t="str">
+        <x:v>CAD symmetry-derived from LF: local Y reflection</x:v>
+      </x:c>
+      <x:c r="P16" s="301" t="str">
+        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q16" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="301" t="str">
+        <x:v>rh_foot_link</x:v>
+      </x:c>
+      <x:c r="B17" s="301" t="str">
+        <x:v>RH</x:v>
+      </x:c>
+      <x:c r="C17" s="301" t="str">
+        <x:v>Foot subassembly</x:v>
+      </x:c>
+      <x:c r="D17" s="303" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="E17" s="303" t="n">
+        <x:v>-0.00052</x:v>
+      </x:c>
+      <x:c r="F17" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="303" t="n">
+        <x:v>0.01548</x:v>
+      </x:c>
+      <x:c r="H17" s="302" t="n">
+        <x:v>0.00000114526961866</x:v>
+      </x:c>
+      <x:c r="I17" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="302" t="n">
+        <x:v>-1.55064671079e-8</x:v>
+      </x:c>
+      <x:c r="K17" s="302" t="n">
+        <x:v>0.00000120267175</x:v>
+      </x:c>
+      <x:c r="L17" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="302" t="n">
+        <x:v>0.00000114835213134</x:v>
+      </x:c>
+      <x:c r="N17" s="301" t="str">
+        <x:v>DERIVED BY SYMMETRY</x:v>
+      </x:c>
+      <x:c r="O17" s="301" t="str">
+        <x:v>CAD symmetry-derived from LF: identical foot geometry</x:v>
+      </x:c>
+      <x:c r="P17" s="301" t="str">
+        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q17" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="301" t="str">
+        <x:v>lh_hip_link</x:v>
+      </x:c>
+      <x:c r="B18" s="301" t="str">
+        <x:v>LH</x:v>
+      </x:c>
+      <x:c r="C18" s="301" t="str">
+        <x:v>Hip subassembly</x:v>
+      </x:c>
+      <x:c r="D18" s="303" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="E18" s="303" t="n">
+        <x:v>0.00366</x:v>
+      </x:c>
+      <x:c r="F18" s="303" t="n">
+        <x:v>0.02982</x:v>
+      </x:c>
+      <x:c r="G18" s="303" t="n">
+        <x:v>0.00694</x:v>
+      </x:c>
+      <x:c r="H18" s="302" t="n">
+        <x:v>0.0000402252347591</x:v>
+      </x:c>
+      <x:c r="I18" s="302" t="n">
+        <x:v>-0.00000131462768927</x:v>
+      </x:c>
+      <x:c r="J18" s="302" t="n">
+        <x:v>-0.00000113953716339</x:v>
+      </x:c>
+      <x:c r="K18" s="302" t="n">
+        <x:v>0.000018958128496</x:v>
+      </x:c>
+      <x:c r="L18" s="302" t="n">
+        <x:v>-0.00000446400670021</x:v>
+      </x:c>
+      <x:c r="M18" s="302" t="n">
+        <x:v>0.0000454280867449</x:v>
+      </x:c>
+      <x:c r="N18" s="301" t="str">
+        <x:v>DERIVED BY SYMMETRY</x:v>
+      </x:c>
+      <x:c r="O18" s="301" t="str">
+        <x:v>CAD symmetry-derived from LF: same left-side local geometry</x:v>
+      </x:c>
+      <x:c r="P18" s="301" t="str">
+        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q18" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="301" t="str">
+        <x:v>lh_upper_leg_link</x:v>
+      </x:c>
+      <x:c r="B19" s="301" t="str">
+        <x:v>LH</x:v>
+      </x:c>
+      <x:c r="C19" s="301" t="str">
+        <x:v>Upper-leg subassembly</x:v>
+      </x:c>
+      <x:c r="D19" s="303" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="E19" s="303" t="n">
+        <x:v>0.00108</x:v>
+      </x:c>
+      <x:c r="F19" s="303" t="n">
+        <x:v>0.00015</x:v>
+      </x:c>
+      <x:c r="G19" s="303" t="n">
+        <x:v>-0.04503</x:v>
+      </x:c>
+      <x:c r="H19" s="302" t="n">
+        <x:v>0.000205436660094</x:v>
+      </x:c>
+      <x:c r="I19" s="302" t="n">
+        <x:v>-5.63507198417e-8</x:v>
+      </x:c>
+      <x:c r="J19" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" s="302" t="n">
+        <x:v>0.000199175976156</x:v>
+      </x:c>
+      <x:c r="L19" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" s="302" t="n">
+        <x:v>0.00003111294525</x:v>
+      </x:c>
+      <x:c r="N19" s="301" t="str">
+        <x:v>DERIVED BY SYMMETRY</x:v>
+      </x:c>
+      <x:c r="O19" s="301" t="str">
+        <x:v>CAD symmetry-derived from LF: same left-side local geometry</x:v>
+      </x:c>
+      <x:c r="P19" s="301" t="str">
+        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q19" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="301" t="str">
+        <x:v>lh_lower_leg_link</x:v>
+      </x:c>
+      <x:c r="B20" s="301" t="str">
+        <x:v>LH</x:v>
+      </x:c>
+      <x:c r="C20" s="301" t="str">
+        <x:v>Lower-leg subassembly</x:v>
+      </x:c>
+      <x:c r="D20" s="303" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="E20" s="303" t="n">
+        <x:v>0.03075</x:v>
+      </x:c>
+      <x:c r="F20" s="303" t="n">
+        <x:v>-0.00118</x:v>
+      </x:c>
+      <x:c r="G20" s="303" t="n">
+        <x:v>-0.01958</x:v>
+      </x:c>
+      <x:c r="H20" s="302" t="n">
+        <x:v>0.0000215172642767</x:v>
+      </x:c>
+      <x:c r="I20" s="302" t="n">
+        <x:v>6.0930015348e-7</x:v>
+      </x:c>
+      <x:c r="J20" s="302" t="n">
+        <x:v>0.0000168302311374</x:v>
+      </x:c>
+      <x:c r="K20" s="302" t="n">
+        <x:v>0.000102530052784</x:v>
+      </x:c>
+      <x:c r="L20" s="302" t="n">
+        <x:v>-3.71953235117e-7</x:v>
+      </x:c>
+      <x:c r="M20" s="302" t="n">
+        <x:v>0.000104321477439</x:v>
+      </x:c>
+      <x:c r="N20" s="301" t="str">
+        <x:v>DERIVED BY SYMMETRY</x:v>
+      </x:c>
+      <x:c r="O20" s="301" t="str">
+        <x:v>CAD symmetry-derived from LF: same left-side local geometry</x:v>
+      </x:c>
+      <x:c r="P20" s="301" t="str">
+        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q20" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="301" t="str">
+        <x:v>lh_foot_link</x:v>
+      </x:c>
+      <x:c r="B21" s="301" t="str">
+        <x:v>LH</x:v>
+      </x:c>
+      <x:c r="C21" s="301" t="str">
+        <x:v>Foot subassembly</x:v>
+      </x:c>
+      <x:c r="D21" s="303" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="E21" s="303" t="n">
+        <x:v>-0.00052</x:v>
+      </x:c>
+      <x:c r="F21" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="303" t="n">
+        <x:v>0.01548</x:v>
+      </x:c>
+      <x:c r="H21" s="302" t="n">
+        <x:v>0.00000114526961866</x:v>
+      </x:c>
+      <x:c r="I21" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J21" s="302" t="n">
+        <x:v>-1.55064671079e-8</x:v>
+      </x:c>
+      <x:c r="K21" s="302" t="n">
+        <x:v>0.00000120267175</x:v>
+      </x:c>
+      <x:c r="L21" s="302" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21" s="302" t="n">
+        <x:v>0.00000114835213134</x:v>
+      </x:c>
+      <x:c r="N21" s="301" t="str">
+        <x:v>DERIVED BY SYMMETRY</x:v>
+      </x:c>
+      <x:c r="O21" s="301" t="str">
+        <x:v>CAD symmetry-derived from LF: identical foot geometry</x:v>
+      </x:c>
+      <x:c r="P21" s="301" t="str">
+        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+      </x:c>
+      <x:c r="Q21" s="301" t="str">
+        <x:v>URDF &lt;inertial&gt; ready</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:Q1"/>
+    <x:mergeCell ref="A2:Q2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="13" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="11" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="11" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="11" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="22" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="56" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="289" t="str">
+        <x:v>MATDOG — Dati CAD sorgente per proprietà fisiche</x:v>
+      </x:c>
+      <x:c r="B1" s="289"/>
+      <x:c r="C1" s="289"/>
+      <x:c r="D1" s="289"/>
+      <x:c r="E1" s="289"/>
+      <x:c r="F1" s="289"/>
+      <x:c r="G1" s="289"/>
+      <x:c r="H1" s="289"/>
+      <x:c r="I1" s="289"/>
+      <x:c r="J1" s="289"/>
+      <x:c r="K1" s="289"/>
+      <x:c r="L1" s="289"/>
+      <x:c r="M1" s="289"/>
+      <x:c r="N1" s="289"/>
+      <x:c r="O1" s="289"/>
+      <x:c r="P1" s="289"/>
+      <x:c r="Q1" s="289"/>
+      <x:c r="R1" s="289"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="294" t="str">
+        <x:v>Trascrizione strutturata dei report Solid Edge ricevuti. I valori di massa per URDF usano la tabella CAD riconciliata; i report per-link visualizzano la massa arrotondata a 0.001 kg.</x:v>
+      </x:c>
+      <x:c r="B2" s="294"/>
+      <x:c r="C2" s="294"/>
+      <x:c r="D2" s="294"/>
+      <x:c r="E2" s="294"/>
+      <x:c r="F2" s="294"/>
+      <x:c r="G2" s="294"/>
+      <x:c r="H2" s="294"/>
+      <x:c r="I2" s="294"/>
+      <x:c r="J2" s="294"/>
+      <x:c r="K2" s="294"/>
+      <x:c r="L2" s="294"/>
+      <x:c r="M2" s="294"/>
+      <x:c r="N2" s="294"/>
+      <x:c r="O2" s="294"/>
+      <x:c r="P2" s="294"/>
+      <x:c r="Q2" s="294"/>
+      <x:c r="R2" s="294"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="305" t="str">
+        <x:v>Source report</x:v>
+      </x:c>
+      <x:c r="B4" s="305" t="str">
+        <x:v>Scope</x:v>
+      </x:c>
+      <x:c r="C4" s="305" t="str">
+        <x:v>Mass reported
+[kg]</x:v>
+      </x:c>
+      <x:c r="D4" s="305" t="str">
+        <x:v>Mass used
+[kg]</x:v>
+      </x:c>
+      <x:c r="E4" s="305" t="str">
+        <x:v>CoM X
+[mm]</x:v>
+      </x:c>
+      <x:c r="F4" s="305" t="str">
+        <x:v>CoM Y
+[mm]</x:v>
+      </x:c>
+      <x:c r="G4" s="305" t="str">
+        <x:v>CoM Z
+[mm]</x:v>
+      </x:c>
+      <x:c r="H4" s="305" t="str">
+        <x:v>Ixx global</x:v>
+      </x:c>
+      <x:c r="I4" s="305" t="str">
+        <x:v>Iyy global</x:v>
+      </x:c>
+      <x:c r="J4" s="305" t="str">
+        <x:v>Izz global</x:v>
+      </x:c>
+      <x:c r="K4" s="305" t="str">
+        <x:v>Ixy product</x:v>
+      </x:c>
+      <x:c r="L4" s="305" t="str">
+        <x:v>Ixz product</x:v>
+      </x:c>
+      <x:c r="M4" s="305" t="str">
+        <x:v>Iyz product</x:v>
+      </x:c>
+      <x:c r="N4" s="305" t="str">
+        <x:v>K1
+[mm]</x:v>
+      </x:c>
+      <x:c r="O4" s="305" t="str">
+        <x:v>K2
+[mm]</x:v>
+      </x:c>
+      <x:c r="P4" s="305" t="str">
+        <x:v>K3
+[mm]</x:v>
+      </x:c>
+      <x:c r="Q4" s="305" t="str">
+        <x:v>Use in REV00</x:v>
+      </x:c>
+      <x:c r="R4" s="305" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="301" t="str">
+        <x:v>physprop__base_link.txt</x:v>
+      </x:c>
+      <x:c r="B5" s="301" t="str">
+        <x:v>base_link</x:v>
+      </x:c>
+      <x:c r="C5" s="306" t="n">
+        <x:v>1.281</x:v>
+      </x:c>
+      <x:c r="D5" s="306" t="n">
+        <x:v>1.282</x:v>
+      </x:c>
+      <x:c r="E5" s="307" t="n">
+        <x:v>5.84</x:v>
+      </x:c>
+      <x:c r="F5" s="307" t="n">
+        <x:v>-0.65</x:v>
+      </x:c>
+      <x:c r="G5" s="307" t="n">
+        <x:v>27.73</x:v>
+      </x:c>
+      <x:c r="H5" s="303" t="n">
+        <x:v>0.246</x:v>
+      </x:c>
+      <x:c r="I5" s="303" t="n">
+        <x:v>0.989</x:v>
+      </x:c>
+      <x:c r="J5" s="303" t="n">
+        <x:v>0.954</x:v>
+      </x:c>
+      <x:c r="K5" s="303" t="n">
+        <x:v>-0.002</x:v>
+      </x:c>
+      <x:c r="L5" s="303" t="n">
+        <x:v>0.065</x:v>
+      </x:c>
+      <x:c r="M5" s="303" t="n">
+        <x:v>-0.002</x:v>
+      </x:c>
+      <x:c r="N5" s="307" t="n">
+        <x:v>86.19</x:v>
+      </x:c>
+      <x:c r="O5" s="307" t="n">
+        <x:v>83.18</x:v>
+      </x:c>
+      <x:c r="P5" s="307" t="n">
+        <x:v>33.61</x:v>
+      </x:c>
+      <x:c r="Q5" s="301" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="R5" s="301" t="str">
+        <x:v>Mass used is the CAD-reconciliation value from weight_breakdown_summary.txt.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="301" t="str">
+        <x:v>physprop__lf_hip_link.txt</x:v>
+      </x:c>
+      <x:c r="B6" s="301" t="str">
+        <x:v>lf_hip_link</x:v>
+      </x:c>
+      <x:c r="C6" s="306" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="D6" s="306" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="E6" s="307" t="n">
+        <x:v>3.66</x:v>
+      </x:c>
+      <x:c r="F6" s="307" t="n">
+        <x:v>29.82</x:v>
+      </x:c>
+      <x:c r="G6" s="307" t="n">
+        <x:v>6.94</x:v>
+      </x:c>
+      <x:c r="H6" s="303" t="n">
+        <x:v>0.009</x:v>
+      </x:c>
+      <x:c r="I6" s="303" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="J6" s="303" t="n">
+        <x:v>0.009</x:v>
+      </x:c>
+      <x:c r="K6" s="303" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="L6" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="303" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="N6" s="307" t="n">
+        <x:v>30.43</x:v>
+      </x:c>
+      <x:c r="O6" s="307" t="n">
+        <x:v>28.35</x:v>
+      </x:c>
+      <x:c r="P6" s="307" t="n">
+        <x:v>19.04</x:v>
+      </x:c>
+      <x:c r="Q6" s="301" t="str">
+        <x:v>Direct LF / symmetry seed</x:v>
+      </x:c>
+      <x:c r="R6" s="301" t="str">
+        <x:v>RF and RH are derived by local Y reflection; LH uses the same left-side local geometry.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="301" t="str">
+        <x:v>physprop__lf_upper_leg_link.txt</x:v>
+      </x:c>
+      <x:c r="B7" s="301" t="str">
+        <x:v>lf_upper_leg_link</x:v>
+      </x:c>
+      <x:c r="C7" s="306" t="n">
+        <x:v>0.172</x:v>
+      </x:c>
+      <x:c r="D7" s="306" t="n">
+        <x:v>0.1725</x:v>
+      </x:c>
+      <x:c r="E7" s="307" t="n">
+        <x:v>1.08</x:v>
+      </x:c>
+      <x:c r="F7" s="307" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="G7" s="307" t="n">
+        <x:v>-45.03</x:v>
+      </x:c>
+      <x:c r="H7" s="303" t="n">
+        <x:v>0.055</x:v>
+      </x:c>
+      <x:c r="I7" s="303" t="n">
+        <x:v>0.055</x:v>
+      </x:c>
+      <x:c r="J7" s="303" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+      <x:c r="K7" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7" s="303" t="n">
+        <x:v>-0.001</x:v>
+      </x:c>
+      <x:c r="M7" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" s="307" t="n">
+        <x:v>34.51</x:v>
+      </x:c>
+      <x:c r="O7" s="307" t="n">
+        <x:v>33.98</x:v>
+      </x:c>
+      <x:c r="P7" s="307" t="n">
+        <x:v>13.43</x:v>
+      </x:c>
+      <x:c r="Q7" s="301" t="str">
+        <x:v>Direct LF / symmetry seed</x:v>
+      </x:c>
+      <x:c r="R7" s="301" t="str">
+        <x:v>RF and RH are derived by local Y reflection; LH uses the same left-side local geometry.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="301" t="str">
+        <x:v>physprop__lf_lower_leg_link.txt</x:v>
+      </x:c>
+      <x:c r="B8" s="301" t="str">
+        <x:v>lf_lower_leg_link</x:v>
+      </x:c>
+      <x:c r="C8" s="306" t="n">
+        <x:v>0.059</x:v>
+      </x:c>
+      <x:c r="D8" s="306" t="n">
+        <x:v>0.0595</x:v>
+      </x:c>
+      <x:c r="E8" s="307" t="n">
+        <x:v>30.75</x:v>
+      </x:c>
+      <x:c r="F8" s="307" t="n">
+        <x:v>-1.18</x:v>
+      </x:c>
+      <x:c r="G8" s="307" t="n">
+        <x:v>-19.58</x:v>
+      </x:c>
+      <x:c r="H8" s="303" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="I8" s="303" t="n">
+        <x:v>0.018</x:v>
+      </x:c>
+      <x:c r="J8" s="303" t="n">
+        <x:v>0.016</x:v>
+      </x:c>
+      <x:c r="K8" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L8" s="303" t="n">
+        <x:v>-0.005</x:v>
+      </x:c>
+      <x:c r="M8" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" s="307" t="n">
+        <x:v>42.53</x:v>
+      </x:c>
+      <x:c r="O8" s="307" t="n">
+        <x:v>41.51</x:v>
+      </x:c>
+      <x:c r="P8" s="307" t="n">
+        <x:v>17.5</x:v>
+      </x:c>
+      <x:c r="Q8" s="301" t="str">
+        <x:v>Direct LF / symmetry seed</x:v>
+      </x:c>
+      <x:c r="R8" s="301" t="str">
+        <x:v>RF and RH are derived by local Y reflection; LH uses the same left-side local geometry.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="301" t="str">
+        <x:v>physprop__lf_foot_link.txt</x:v>
+      </x:c>
+      <x:c r="B9" s="301" t="str">
+        <x:v>lf_foot_link</x:v>
+      </x:c>
+      <x:c r="C9" s="306" t="n">
+        <x:v>0.017</x:v>
+      </x:c>
+      <x:c r="D9" s="306" t="n">
+        <x:v>0.0175</x:v>
+      </x:c>
+      <x:c r="E9" s="307" t="n">
+        <x:v>-0.52</x:v>
+      </x:c>
+      <x:c r="F9" s="307" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="307" t="n">
+        <x:v>15.48</x:v>
+      </x:c>
+      <x:c r="H9" s="303" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="I9" s="303" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="J9" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" s="307" t="n">
+        <x:v>8.29</x:v>
+      </x:c>
+      <x:c r="O9" s="307" t="n">
+        <x:v>8.15</x:v>
+      </x:c>
+      <x:c r="P9" s="307" t="n">
+        <x:v>8.04</x:v>
+      </x:c>
+      <x:c r="Q9" s="301" t="str">
+        <x:v>Direct LF / identical foot seed</x:v>
+      </x:c>
+      <x:c r="R9" s="301" t="str">
+        <x:v>All four foot links use the identical CAD foot geometry.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="301" t="str">
+        <x:v>physprop__robotdog_assembly.txt</x:v>
+      </x:c>
+      <x:c r="B10" s="301" t="str">
+        <x:v>17-link assembly</x:v>
+      </x:c>
+      <x:c r="C10" s="306" t="n">
+        <x:v>2.48</x:v>
+      </x:c>
+      <x:c r="D10" s="306" t="n">
+        <x:v>2.48</x:v>
+      </x:c>
+      <x:c r="E10" s="307" t="n">
+        <x:v>9.48</x:v>
+      </x:c>
+      <x:c r="F10" s="307" t="n">
+        <x:v>-0.71</x:v>
+      </x:c>
+      <x:c r="G10" s="307" t="n">
+        <x:v>5.91</x:v>
+      </x:c>
+      <x:c r="H10" s="303" t="n">
+        <x:v>0.016</x:v>
+      </x:c>
+      <x:c r="I10" s="303" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="J10" s="303" t="n">
+        <x:v>0.037</x:v>
+      </x:c>
+      <x:c r="K10" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10" s="303" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="M10" s="303" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" s="307" t="n">
+        <x:v>121.31</x:v>
+      </x:c>
+      <x:c r="O10" s="307" t="n">
+        <x:v>108.92</x:v>
+      </x:c>
+      <x:c r="P10" s="307" t="n">
+        <x:v>80.42</x:v>
+      </x:c>
+      <x:c r="Q10" s="301" t="str">
+        <x:v>Aggregate validation</x:v>
+      </x:c>
+      <x:c r="R10" s="301" t="str">
+        <x:v>User notes that the neck yaw actuator is not represented by this assembly scope; no standalone neck link is added to REV00.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:R1"/>
+    <x:mergeCell ref="A2:R2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/03_CAD/URDF/matt_robodog_rev00/reference/Coordinate_Cinematiche_matt_robodog_rev00.xlsx
+++ b/03_CAD/URDF/matt_robodog_rev00/reference/Coordinate_Cinematiche_matt_robodog_rev00.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Joint_Parameters" sheetId="1" r:id="R1aef14a5ec6a4b2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mesh_Transforms" sheetId="2" r:id="R55c82896a21a4ba6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Notes" sheetId="3" r:id="Rbf13f7eeb9bc484d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Link_Engineering" sheetId="4" r:id="R4f9575abea25442e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mass_Summary" sheetId="5" r:id="Rbb5f3fdc6baa40a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engineering_Weight_Source" sheetId="6" r:id="R58c9dcc699854f93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="URDF_Audit" sheetId="7" r:id="R36b9bd6648a0444c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inertial_Properties" sheetId="8" r:id="Rc52f2c3cd0764fe5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAD_Source_Data" sheetId="9" r:id="Re29c0b12f341438a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mass_Reconciliation" sheetId="10" r:id="Rf788816304f64b13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physical_Property_Method" sheetId="11" r:id="Re58eb096c8f14ec6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Joint_Parameters" sheetId="1" r:id="R17117f0308514131"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mesh_Transforms" sheetId="2" r:id="R8f9d7fc1e4104cc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Notes" sheetId="3" r:id="R08f3f5507a8d421a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Link_Engineering" sheetId="4" r:id="R1bd136d64b484fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mass_Summary" sheetId="5" r:id="R01b5bfde62b3429e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engineering_Weight_Source" sheetId="6" r:id="R47e07315701e4e75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="URDF_Audit" sheetId="7" r:id="Rf3337a77e49544ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inertial_Properties" sheetId="8" r:id="R50c7af26ae824333"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAD_Source_Data" sheetId="9" r:id="R3df41296733f4968"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mass_Reconciliation" sheetId="10" r:id="R00897d6d28824d0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physical_Property_Method" sheetId="11" r:id="Rada7cf4125ca4620"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -319,7 +319,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="393">
+  <x:cellXfs count="405">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1316,6 +1316,38 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="19" fillId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -2978,7 +3010,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ecf6a50657d4585"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R783632fb57ee4927"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3484,61 +3516,73 @@
     <x:col min="21" max="21" width="22" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="22" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="22" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="16" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="18" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="13" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="17" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="289" t="str">
-        <x:v>MATDOG — Mesh Visual + Collision + proprietà dinamiche</x:v>
-      </x:c>
-      <x:c r="B1" s="289"/>
-      <x:c r="C1" s="289"/>
-      <x:c r="D1" s="289"/>
-      <x:c r="E1" s="289"/>
-      <x:c r="F1" s="289"/>
-      <x:c r="G1" s="289"/>
-      <x:c r="H1" s="289"/>
-      <x:c r="I1" s="289"/>
-      <x:c r="J1" s="289"/>
-      <x:c r="K1" s="289"/>
-      <x:c r="L1" s="289"/>
-      <x:c r="M1" s="289"/>
-      <x:c r="N1" s="289"/>
-      <x:c r="O1" s="289"/>
-      <x:c r="P1" s="289"/>
-      <x:c r="Q1" s="289"/>
-      <x:c r="R1" s="289"/>
-      <x:c r="S1" s="289"/>
-      <x:c r="T1" s="289"/>
-      <x:c r="U1" s="289"/>
-      <x:c r="V1" s="289"/>
-      <x:c r="W1" s="289"/>
+      <x:c r="A1" s="404" t="str">
+        <x:v>MATDOG — Mesh visual + collision + proprietà dinamiche · STL mm → URDF m</x:v>
+      </x:c>
+      <x:c r="B1" s="404"/>
+      <x:c r="C1" s="404"/>
+      <x:c r="D1" s="404"/>
+      <x:c r="E1" s="404"/>
+      <x:c r="F1" s="404"/>
+      <x:c r="G1" s="404"/>
+      <x:c r="H1" s="404"/>
+      <x:c r="I1" s="404"/>
+      <x:c r="J1" s="404"/>
+      <x:c r="K1" s="404"/>
+      <x:c r="L1" s="404"/>
+      <x:c r="M1" s="404"/>
+      <x:c r="N1" s="404"/>
+      <x:c r="O1" s="404"/>
+      <x:c r="P1" s="404"/>
+      <x:c r="Q1" s="404"/>
+      <x:c r="R1" s="404"/>
+      <x:c r="S1" s="404"/>
+      <x:c r="T1" s="404"/>
+      <x:c r="U1" s="404"/>
+      <x:c r="V1" s="404"/>
+      <x:c r="W1" s="404"/>
+      <x:c r="X1" s="156"/>
+      <x:c r="Y1" s="156"/>
+      <x:c r="Z1" s="156"/>
+      <x:c r="AA1" s="156"/>
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
-      <x:c r="A2" s="294" t="str">
-        <x:v>Origini mesh visual/collision: xyz = 0,0,0 m · rpy = 0°,0°,0°. Le colonne di massa e stato inerziale sono aggiornate dal modello CAD dinamico REV00.</x:v>
-      </x:c>
-      <x:c r="B2" s="294"/>
-      <x:c r="C2" s="294"/>
-      <x:c r="D2" s="294"/>
-      <x:c r="E2" s="294"/>
-      <x:c r="F2" s="294"/>
-      <x:c r="G2" s="294"/>
-      <x:c r="H2" s="294"/>
-      <x:c r="I2" s="294"/>
-      <x:c r="J2" s="294"/>
-      <x:c r="K2" s="294"/>
-      <x:c r="L2" s="294"/>
-      <x:c r="M2" s="294"/>
-      <x:c r="N2" s="294"/>
-      <x:c r="O2" s="294"/>
-      <x:c r="P2" s="294"/>
-      <x:c r="Q2" s="294"/>
-      <x:c r="R2" s="294"/>
-      <x:c r="S2" s="294"/>
-      <x:c r="T2" s="294"/>
-      <x:c r="U2" s="294"/>
-      <x:c r="V2" s="294"/>
-      <x:c r="W2" s="294"/>
+      <x:c r="A2" s="399" t="str">
+        <x:v>Origini mesh visual/collision: xyz = 0,0,0 m · rpy = 0°,0°,0°. Gli STL CAD restano in millimetri; ogni &lt;mesh&gt; URDF applica scale="0.001 0.001 0.001".</x:v>
+      </x:c>
+      <x:c r="B2" s="399"/>
+      <x:c r="C2" s="399"/>
+      <x:c r="D2" s="399"/>
+      <x:c r="E2" s="399"/>
+      <x:c r="F2" s="399"/>
+      <x:c r="G2" s="399"/>
+      <x:c r="H2" s="399"/>
+      <x:c r="I2" s="399"/>
+      <x:c r="J2" s="399"/>
+      <x:c r="K2" s="399"/>
+      <x:c r="L2" s="399"/>
+      <x:c r="M2" s="399"/>
+      <x:c r="N2" s="399"/>
+      <x:c r="O2" s="399"/>
+      <x:c r="P2" s="399"/>
+      <x:c r="Q2" s="399"/>
+      <x:c r="R2" s="399"/>
+      <x:c r="S2" s="399"/>
+      <x:c r="T2" s="399"/>
+      <x:c r="U2" s="399"/>
+      <x:c r="V2" s="399"/>
+      <x:c r="W2" s="399"/>
+      <x:c r="X2" s="156"/>
+      <x:c r="Y2" s="156"/>
+      <x:c r="Z2" s="156"/>
+      <x:c r="AA2" s="156"/>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="345" t="str">
@@ -3624,6 +3668,20 @@
       <x:c r="W5" s="345" t="str">
         <x:v>URDF metadata</x:v>
       </x:c>
+      <x:c r="X5" s="156" t="str">
+        <x:v>Visual scale
+[STL → URDF]</x:v>
+      </x:c>
+      <x:c r="Y5" s="156" t="str">
+        <x:v>Collision scale
+[STL → URDF]</x:v>
+      </x:c>
+      <x:c r="Z5" s="156" t="str">
+        <x:v>STL source unit</x:v>
+      </x:c>
+      <x:c r="AA5" s="156" t="str">
+        <x:v>URDF geometry unit</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="19" customHeight="1">
       <x:c r="A6" s="359" t="str">
@@ -3693,7 +3751,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W6" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X6" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y6" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z6" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA6" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="19" customHeight="1">
@@ -3764,7 +3834,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W7" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X7" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y7" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z7" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA7" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="19" customHeight="1">
@@ -3835,7 +3917,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W8" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X8" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y8" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z8" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA8" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="19" customHeight="1">
@@ -3906,7 +4000,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W9" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X9" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y9" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z9" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA9" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="19" customHeight="1">
@@ -3977,7 +4083,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W10" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X10" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y10" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z10" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA10" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="19" customHeight="1">
@@ -4048,7 +4166,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W11" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X11" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y11" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z11" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA11" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="19" customHeight="1">
@@ -4119,7 +4249,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W12" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X12" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y12" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z12" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA12" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="19" customHeight="1">
@@ -4190,7 +4332,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W13" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X13" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y13" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z13" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA13" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="19" customHeight="1">
@@ -4261,7 +4415,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W14" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X14" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y14" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z14" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA14" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="19" customHeight="1">
@@ -4332,7 +4498,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W15" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X15" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y15" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z15" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA15" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="19" customHeight="1">
@@ -4403,7 +4581,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W16" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X16" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y16" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z16" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA16" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="19" customHeight="1">
@@ -4474,7 +4664,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W17" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X17" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y17" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z17" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA17" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="19" customHeight="1">
@@ -4545,7 +4747,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W18" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X18" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y18" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z18" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA18" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="19" customHeight="1">
@@ -4616,7 +4830,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W19" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X19" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y19" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z19" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA19" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="19" customHeight="1">
@@ -4687,7 +4913,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W20" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X20" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y20" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z20" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA20" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="19" customHeight="1">
@@ -4758,7 +4996,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W21" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X21" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y21" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z21" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA21" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="19" customHeight="1">
@@ -4829,7 +5079,19 @@
         <x:v>URDF &lt;inertial&gt; inserted</x:v>
       </x:c>
       <x:c r="W22" s="301" t="str">
-        <x:v>Simulation-ready</x:v>
+        <x:v>Simulation-ready · mesh scale=0.001</x:v>
+      </x:c>
+      <x:c r="X22" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Y22" s="156" t="str">
+        <x:v>0.001 0.001 0.001</x:v>
+      </x:c>
+      <x:c r="Z22" s="156" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="AA22" s="156" t="str">
+        <x:v>m</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4892,7 +5154,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94ad51e75eba4da9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb06a6cc5bb6411d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4944,16 +5206,18 @@
         <x:v>File URDF finale</x:v>
       </x:c>
       <x:c r="B5" s="43" t="str">
-        <x:v>matt_robodog_rev00_final_kinematics_mass_material_lowerlimit92_clean.urdf</x:v>
-      </x:c>
+        <x:v>matt_robodog_rev00.urdf</x:v>
+      </x:c>
+      <x:c r="C5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="90" t="str">
         <x:v>Stato</x:v>
       </x:c>
       <x:c r="B6" s="95" t="str">
-        <x:v>Baseline cinematica approvata</x:v>
-      </x:c>
+        <x:v>Baseline cinematica + dinamica + scala mesh approvata</x:v>
+      </x:c>
+      <x:c r="C6"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="100" t="str">
@@ -5062,6 +5326,17 @@
       <x:c r="F14" s="115"/>
       <x:c r="G14" s="115"/>
       <x:c r="H14" s="115"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Unità mesh STL</x:v>
+      </x:c>
+      <x:c r="C15" s="156" t="str">
+        <x:v>Vertici STL esportati dal CAD in mm. In ogni mesh visual e collision URDF: scale="0.001 0.001 0.001"; joint, CoM e inerzie restano in unità SI.</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="121" t="str">
@@ -5923,7 +6198,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R019e2d942cee4562"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e033e6dd49543d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7413,7 +7688,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="294" t="str">
-        <x:v>Audit aggiornato: struttura, riferimenti mesh, origini visual/collision, limiti, masse CAD, CoM per-link e tensori d’inerzia.</x:v>
+        <x:v>Audit aggiornato: struttura, joint, mesh, scala STL mm→m, limiti, masse CAD, CoM per-link e tensori d’inerzia.</x:v>
       </x:c>
       <x:c r="B2" s="294"/>
       <x:c r="C2" s="294"/>
@@ -7530,13 +7805,13 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C10" s="301" t="str">
-        <x:v>34 riferimenti mesh (visual + collision), tutti relativi a meshes/*.stl; 17 asset unici.</x:v>
+        <x:v>34 riferimenti mesh (visual + collision), tutti relativi a meshes/*.stl; 17 asset unici; ogni mesh dichiara scale="0.001 0.001 0.001".</x:v>
       </x:c>
       <x:c r="D10" s="301" t="str">
-        <x:v>Nessuna.</x:v>
+        <x:v>Scala URDF dichiarata per STL CAD in mm.</x:v>
       </x:c>
       <x:c r="E10" s="301" t="str">
-        <x:v>Pulito</x:v>
+        <x:v>Canonico</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="38" customHeight="1">
